--- a/data/CHE447_27.xlsx
+++ b/data/CHE447_27.xlsx
@@ -13,14 +13,14 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId9" roundtripDataChecksum="dA20AQgcLlbyyI1nokrOvN4X2M3M6ZFBolK7X74yrI8="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId9" roundtripDataChecksum="epzxWdUrILpl+aBWVdXvcPy7Iku+rGhBAQ9sdo5Su3Q="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="172">
   <si>
     <t>Global Assumptions and Thresholds</t>
   </si>
@@ -376,6 +376,9 @@
     <t>Q_noticeable_melt_J</t>
   </si>
   <si>
+    <t>Deff_eff_m2_s</t>
+  </si>
+  <si>
     <t>M_abs_1800_g</t>
   </si>
   <si>
@@ -448,6 +451,15 @@
     <t>t_finish_s</t>
   </si>
   <si>
+    <t>m_cone_dry_g</t>
+  </si>
+  <si>
+    <t>M_abs_notice_g</t>
+  </si>
+  <si>
+    <t>M_abs_bad_g</t>
+  </si>
+  <si>
     <t>Source Register</t>
   </si>
   <si>
@@ -515,6 +527,42 @@
   </si>
   <si>
     <t>https://openresearch.surrey.ac.uk/view/pdfCoverPage?download=true&amp;filePid=13161200050002346&amp;instCode=44SUR_INST</t>
+  </si>
+  <si>
+    <t>Parameter Setting Rationale for Ice Cream and Cone Types
+To keep the case matrix physically meaningful while still manageable for a 27-run design, we grouped the inputs into ice cream type and cone type rather than varying every material property independently. For the ice cream, density was used as the main structural indicator because it is directly tied to overrun: standard ice cream is commonly close to about 550 kg/m3, while more airy products are lighter and denser premium-style products are heavier. Based on this logic, we used three representative ice-cream types: Light/Airy ρice =500 kg/m3, Standard 550 kg/m3, and Dense/Premium 600 kg/m3. We fixed Cp,ice =2750 J/(kg  K) using published frozendessert thermal-property tables, and we assigned effective melting-energy values of 186, 200, and 204 kJ/kg to the three types. These latent-heat values are anchored to published frozen-dessert thermal-property data, while the mapping from "airy/standard/dense" to those three levels is a literature-informed scenario binding rather than a direct product-specific measurement.
+For the cone, thickness and moisture-uptake behavior were treated separately. Cone thickness was assigned three levels, 2.58,2.68, and 2.77 mm , because experimental waffle-cone data report a thickness range of approximately 2.58−2.77 mm. This makes the thickness levels literatureanchored. 
+By contrast, the cone moisture parameter was renamed as Deff,cone  and treated as an effective calibrated parameter, not as a direct thickness-derived constant. This choice was made because moisture-migration studies on manufactured ice-cream cones show that effective diffusivity is strongly influenced by the material/barrier system and operating condition, and may vary over orders of magnitude. In other words, a thicker cone already changes the transport path length geometrically, while Deff,cone  should represent the combined barrier and pore-structure behavior of the cone system. Therefore, Deff,cone  was not mechanically tied to thickness. Instead, we used three engineering levels, 5×10−12,2×10−11, and 6×10−11 m2/s, to span slower to faster uptake behavior within the order of magnitude suggested by cone moisture-migration literature. These values should be interpreted as effective scenario levels to be refined by experiment, not as exact product constants.</t>
+  </si>
+  <si>
+    <t>Cp_ice   = 2750[J/(kg*K)]
+rho_cone = 200[kg/m^3]
+k_cone   = 0.10[W/(m*K)]
+Cp_cone  = 1750[J/(kg*K)]
+eps_cone = 0.80</t>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t xml:space="preserve">Wafer product density range:
+https://ebooks.inflibnet.ac.in/ftp5/chapter/technology-of-wafer-biscuits/1000/
+Waffle cone thickness / weight / moisture:
+https://www.thepharmajournal.com/archives/2023/vol12issue7/PartAB/12-7-58-979.pdf
+Cone moisture migration / effective diffusivity / crispness threshold:
+https://openresearch.surrey.ac.uk/view/pdfCoverPage?download=true&amp;filePid=13161200050002346&amp;instCode=44SUR_INST
+Wafer crispness / water activity / moisture relation:
+https://www.mdpi.com/2076-3417/12/14/7163
+Bakery proxy values for thermal properties:
+https://www.academia.edu/20246150/Determination_of_the_thermal_diffusivity_of_bread_as_a_function_of_porosity
+</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF1155CC"/>
+        <u/>
+      </rPr>
+      <t>https://www.aensiweb.com/old/jasr/jasr/2010/1680-1686.pdf</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -525,7 +573,7 @@
     <numFmt numFmtId="164" formatCode="0.0000E+00"/>
     <numFmt numFmtId="165" formatCode="0.000"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="8">
     <font>
       <sz val="11.0"/>
       <color theme="1"/>
@@ -550,13 +598,21 @@
       <name val="Calibri"/>
     </font>
     <font>
-      <b/>
       <sz val="11.0"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <color rgb="FF0000FF"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -573,18 +629,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFF2CC"/>
         <bgColor rgb="FFFFF2CC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F4E78"/>
-        <bgColor rgb="FF1F4E78"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD9EAF7"/>
-        <bgColor rgb="FFD9EAF7"/>
       </patternFill>
     </fill>
   </fills>
@@ -638,7 +682,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="33">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -659,6 +703,15 @@
     <xf borderId="4" fillId="0" fontId="3" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf borderId="4" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
     <xf borderId="4" fillId="2" fontId="4" numFmtId="2" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -671,19 +724,40 @@
     <xf borderId="4" fillId="0" fontId="3" numFmtId="11" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="4" fillId="3" fontId="3" numFmtId="11" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="4" fillId="2" fontId="4" numFmtId="2" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="4" fillId="0" fontId="3" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="4" fillId="2" fontId="4" numFmtId="11" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="4" fillId="3" fontId="5" numFmtId="11" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="4" fillId="0" fontId="5" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="4" fillId="3" fontId="3" numFmtId="2" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="4" fillId="0" fontId="5" numFmtId="2" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf borderId="4" fillId="3" fontId="5" numFmtId="2" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
     <xf borderId="4" fillId="3" fontId="3" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="4" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="4" fillId="3" fontId="3" numFmtId="2" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="2" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="2" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="4" fillId="3" fontId="3" numFmtId="11" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="4" fillId="0" fontId="3" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf borderId="4" fillId="3" fontId="3" numFmtId="11" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
@@ -695,11 +769,14 @@
     <xf borderId="4" fillId="3" fontId="3" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="1" fillId="4" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="5" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4696,8 +4773,8 @@
     <col customWidth="1" min="15" max="15" width="14.0"/>
     <col customWidth="1" min="16" max="16" width="16.0"/>
     <col customWidth="1" min="17" max="17" width="20.0"/>
-    <col customWidth="1" min="18" max="18" width="10.0"/>
-    <col customWidth="1" min="19" max="19" width="12.0"/>
+    <col customWidth="1" min="18" max="18" width="11.57"/>
+    <col customWidth="1" min="19" max="19" width="13.86"/>
     <col customWidth="1" min="20" max="20" width="16.71"/>
     <col customWidth="1" min="21" max="21" width="16.14"/>
     <col customWidth="1" min="22" max="22" width="15.29"/>
@@ -4726,7 +4803,9 @@
     <col customWidth="1" min="45" max="45" width="16.43"/>
     <col customWidth="1" min="46" max="46" width="22.43"/>
     <col customWidth="1" min="47" max="47" width="12.0"/>
-    <col customWidth="1" min="48" max="48" width="24.0"/>
+    <col customWidth="1" min="48" max="48" width="17.29"/>
+    <col customWidth="1" min="49" max="49" width="15.43"/>
+    <col customWidth="1" min="50" max="50" width="16.43"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4778,8 +4857,10 @@
       <c r="AR1" s="2"/>
       <c r="AS1" s="2"/>
       <c r="AT1" s="2"/>
-      <c r="AU1" s="2"/>
-      <c r="AV1" s="3"/>
+      <c r="AU1" s="3"/>
+      <c r="AV1" s="8"/>
+      <c r="AW1" s="8"/>
+      <c r="AX1" s="8"/>
     </row>
     <row r="3">
       <c r="A3" s="4" t="s">
@@ -4836,8 +4917,8 @@
       <c r="R3" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="S3" s="4" t="s">
-        <v>51</v>
+      <c r="S3" s="9" t="s">
+        <v>118</v>
       </c>
       <c r="T3" s="4" t="s">
         <v>103</v>
@@ -4849,82 +4930,88 @@
         <v>98</v>
       </c>
       <c r="W3" s="4" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="X3" s="4" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="Y3" s="4" t="s">
         <v>87</v>
       </c>
       <c r="Z3" s="4" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="AA3" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="AB3" s="4" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AC3" s="4" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="AD3" s="4" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AE3" s="4" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="AF3" s="4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AG3" s="4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AH3" s="4" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="AI3" s="4" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="AJ3" s="4" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="AK3" s="4" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="AL3" s="4" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="AM3" s="4" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="AN3" s="4" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="AO3" s="4" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AP3" s="4" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="AQ3" s="4" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="AR3" s="4" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AS3" s="4" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="AT3" s="4" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="AU3" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="AV3" s="4" t="s">
-        <v>5</v>
+        <v>142</v>
+      </c>
+      <c r="AV3" s="10" t="s">
+        <v>143</v>
+      </c>
+      <c r="AW3" s="10" t="s">
+        <v>144</v>
+      </c>
+      <c r="AX3" s="10" t="s">
+        <v>145</v>
       </c>
     </row>
     <row r="4">
@@ -4943,25 +5030,25 @@
       <c r="E4" s="5">
         <v>1.0</v>
       </c>
-      <c r="F4" s="8">
+      <c r="F4" s="11">
         <v>293.15</v>
       </c>
-      <c r="G4" s="8">
+      <c r="G4" s="11">
         <v>5.0</v>
       </c>
-      <c r="H4" s="9" t="s">
+      <c r="H4" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="I4" s="9">
+      <c r="I4" s="12">
         <v>500.0</v>
       </c>
-      <c r="J4" s="9">
+      <c r="J4" s="12">
         <v>2750.0</v>
       </c>
-      <c r="K4" s="10">
+      <c r="K4" s="13">
         <v>186000.0</v>
       </c>
-      <c r="L4" s="11">
+      <c r="L4" s="14">
         <f>Assumptions!$B$6</f>
         <v>0.00016558</v>
       </c>
@@ -4981,108 +5068,119 @@
         <f t="shared" ref="P4:P30" si="2">N4+(O4/1000)*K4</f>
         <v>3206.725</v>
       </c>
-      <c r="Q4" s="9" t="s">
+      <c r="Q4" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="R4" s="8">
-        <v>2.6</v>
-      </c>
-      <c r="S4" s="10">
-        <v>2.0E-10</v>
-      </c>
-      <c r="T4" s="12">
-        <v>1.5359E-5</v>
-      </c>
-      <c r="U4" s="12">
-        <v>2.18E-6</v>
-      </c>
-      <c r="V4" s="12">
-        <v>8.7199E-4</v>
-      </c>
-      <c r="W4" s="13">
+      <c r="R4" s="15">
+        <v>2.58</v>
+      </c>
+      <c r="S4" s="16">
+        <v>5.0E-12</v>
+      </c>
+      <c r="T4" s="17">
+        <v>1.5219E-5</v>
+      </c>
+      <c r="U4" s="17">
+        <v>1.3264E-6</v>
+      </c>
+      <c r="V4" s="17">
+        <v>0.0010611</v>
+      </c>
+      <c r="W4" s="18">
         <f t="shared" ref="W4:W30" si="3">IF(V4="","",V4*1000)</f>
-        <v>0.87199</v>
-      </c>
-      <c r="X4" s="13">
+        <v>1.0611</v>
+      </c>
+      <c r="X4" s="18">
         <f t="shared" ref="X4:X30" si="4">IF(OR(U4="",T4=""),"",U4/T4)</f>
-        <v>0.141936324</v>
-      </c>
-      <c r="Y4" s="12">
-        <v>2930.3</v>
-      </c>
-      <c r="Z4" s="6">
+        <v>0.08715421513</v>
+      </c>
+      <c r="Y4" s="17">
+        <v>2934.3</v>
+      </c>
+      <c r="Z4" s="19">
         <f t="shared" ref="Z4:Z30" si="5">IF(OR(Y4="",N4="",K4=""),"",MAX(0,(Y4-N4)/K4)*1000)</f>
-        <v>3.513844086</v>
-      </c>
-      <c r="AA4" s="14">
+        <v>3.535349462</v>
+      </c>
+      <c r="AA4" s="20">
+        <v>1280.0</v>
+      </c>
+      <c r="AB4" s="17">
+        <v>2254.5</v>
+      </c>
+      <c r="AC4" s="20">
         <v>1300.0</v>
       </c>
-      <c r="AB4" s="12">
-        <v>2270.1</v>
-      </c>
-      <c r="AC4" s="14">
-        <v>1320.0</v>
-      </c>
-      <c r="AD4" s="12">
-        <v>2298.6</v>
-      </c>
-      <c r="AE4" s="6">
+      <c r="AD4" s="17">
+        <v>2282.1</v>
+      </c>
+      <c r="AE4" s="19">
         <f t="shared" ref="AE4:AE30" si="6">IF(OR(AA4="",AB4="",AC4="",AD4=""),"",AA4+(N4-AB4)/(AD4-AB4)*(AC4-AA4))</f>
-        <v>1304.649123</v>
-      </c>
-      <c r="AF4" s="14">
+        <v>1296.105072</v>
+      </c>
+      <c r="AF4" s="20">
         <v>2040.0</v>
       </c>
-      <c r="AG4" s="12">
-        <v>3198.2</v>
-      </c>
-      <c r="AH4" s="14">
+      <c r="AG4" s="17">
+        <v>3184.7</v>
+      </c>
+      <c r="AH4" s="20">
         <v>2060.0</v>
       </c>
-      <c r="AI4" s="12">
-        <v>3220.8</v>
-      </c>
-      <c r="AJ4" s="6">
+      <c r="AI4" s="17">
+        <v>3207.3</v>
+      </c>
+      <c r="AJ4" s="19">
         <f t="shared" ref="AJ4:AJ30" si="7">IF(OR(AF4="",AG4="",AH4="",AI4=""),"",AF4+(P4-AG4)/(AI4-AG4)*(AH4-AF4))</f>
-        <v>2047.544248</v>
-      </c>
-      <c r="AK4" s="14">
-        <v>1380.0</v>
-      </c>
-      <c r="AL4" s="15">
-        <v>0.58479</v>
-      </c>
-      <c r="AM4" s="14">
-        <v>1400.0</v>
-      </c>
-      <c r="AN4" s="15">
-        <v>0.60068</v>
+        <v>2059.49115</v>
+      </c>
+      <c r="AK4" s="20">
+        <v>1293.7</v>
+      </c>
+      <c r="AL4" s="21">
+        <v>0.11762</v>
+      </c>
+      <c r="AM4" s="22">
+        <v>1293.8</v>
+      </c>
+      <c r="AN4" s="21">
+        <v>0.12938</v>
       </c>
       <c r="AO4" s="6">
         <f>IF(OR(AK4="",AL4="",AM4="",AN4=""),"",AK4+(Assumptions!$B$8-AL4)/(AN4-AL4)*(AM4-AK4))</f>
-        <v>1399.144116</v>
-      </c>
-      <c r="AP4" s="14">
-        <v>1680.0</v>
-      </c>
-      <c r="AQ4" s="15">
-        <v>0.79783</v>
-      </c>
-      <c r="AR4" s="14">
-        <v>1700.0</v>
-      </c>
-      <c r="AS4" s="15">
-        <v>0.81055</v>
+        <v>1297.801871</v>
+      </c>
+      <c r="AP4" s="22">
+        <v>1294.7</v>
+      </c>
+      <c r="AQ4" s="21">
+        <v>0.25835</v>
+      </c>
+      <c r="AR4" s="22">
+        <v>1294.8</v>
+      </c>
+      <c r="AS4" s="21">
+        <v>0.27523</v>
       </c>
       <c r="AT4" s="6">
         <f>IF(OR(AP4="",AQ4="",AR4="",AS4=""),"",AP4+(Assumptions!$B$9-AQ4)/(AS4-AQ4)*(AR4-AP4))</f>
-        <v>1683.41195</v>
+        <v>1297.908827</v>
       </c>
       <c r="AU4" s="6">
         <f t="shared" ref="AU4:AU30" si="8">IF(AND(AJ4="",AO4=""),"",IF(AJ4="",AO4,IF(AO4="",AJ4,MIN(AJ4,AO4))))</f>
-        <v>1399.144116</v>
-      </c>
-      <c r="AV4" s="16"/>
+        <v>1297.801871</v>
+      </c>
+      <c r="AV4" s="23">
+        <f t="shared" ref="AV4:AV30" si="9">200000 * T4</f>
+        <v>3.0438</v>
+      </c>
+      <c r="AW4" s="23">
+        <f t="shared" ref="AW4:AW30" si="10">0.075*AV4</f>
+        <v>0.228285</v>
+      </c>
+      <c r="AX4" s="24">
+        <f t="shared" ref="AX4:AX30" si="11">0.225*AV4</f>
+        <v>0.684855</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="5">
@@ -5100,25 +5198,25 @@
       <c r="E5" s="5">
         <v>2.0</v>
       </c>
-      <c r="F5" s="8">
+      <c r="F5" s="11">
         <v>293.15</v>
       </c>
-      <c r="G5" s="8">
+      <c r="G5" s="11">
         <v>5.0</v>
       </c>
-      <c r="H5" s="9" t="s">
+      <c r="H5" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="I5" s="9">
+      <c r="I5" s="12">
         <v>550.0</v>
       </c>
-      <c r="J5" s="9">
+      <c r="J5" s="12">
         <v>2750.0</v>
       </c>
-      <c r="K5" s="10">
+      <c r="K5" s="13">
         <v>200000.0</v>
       </c>
-      <c r="L5" s="11">
+      <c r="L5" s="14">
         <f>Assumptions!$B$6</f>
         <v>0.00016558</v>
       </c>
@@ -5138,68 +5236,119 @@
         <f t="shared" si="2"/>
         <v>3504.3975</v>
       </c>
-      <c r="Q5" s="9" t="s">
+      <c r="Q5" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="R5" s="8">
-        <v>2.7</v>
-      </c>
-      <c r="S5" s="10">
-        <v>1.0E-10</v>
-      </c>
-      <c r="T5" s="17"/>
-      <c r="U5" s="17"/>
-      <c r="V5" s="17"/>
-      <c r="W5" s="13" t="str">
+      <c r="R5" s="15">
+        <v>2.68</v>
+      </c>
+      <c r="S5" s="16">
+        <v>6.0E-11</v>
+      </c>
+      <c r="T5" s="17">
+        <v>1.5923E-5</v>
+      </c>
+      <c r="U5" s="25">
+        <v>1.6256E-6</v>
+      </c>
+      <c r="V5" s="17">
+        <v>6.1873E-4</v>
+      </c>
+      <c r="W5" s="26">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="X5" s="13" t="str">
+        <v>0.61873</v>
+      </c>
+      <c r="X5" s="26">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="Y5" s="17"/>
-      <c r="Z5" s="6" t="str">
+        <v>0.1020913145</v>
+      </c>
+      <c r="Y5" s="25">
+        <v>2995.8</v>
+      </c>
+      <c r="Z5" s="6">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="AA5" s="18"/>
-      <c r="AB5" s="17"/>
-      <c r="AC5" s="18"/>
-      <c r="AD5" s="17"/>
-      <c r="AE5" s="6" t="str">
+        <v>2.4570125</v>
+      </c>
+      <c r="AA5" s="22">
+        <v>1420.0</v>
+      </c>
+      <c r="AB5" s="25">
+        <v>2483.5</v>
+      </c>
+      <c r="AC5" s="22">
+        <v>1440.0</v>
+      </c>
+      <c r="AD5" s="25">
+        <v>2511.7</v>
+      </c>
+      <c r="AE5" s="6">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="AF5" s="18"/>
-      <c r="AG5" s="17"/>
-      <c r="AH5" s="18"/>
-      <c r="AI5" s="17"/>
-      <c r="AJ5" s="6" t="str">
+        <v>1434.820922</v>
+      </c>
+      <c r="AF5" s="22">
+        <v>2240.0</v>
+      </c>
+      <c r="AG5" s="25">
+        <v>3504.2</v>
+      </c>
+      <c r="AH5" s="22">
+        <v>2260.0</v>
+      </c>
+      <c r="AI5" s="25">
+        <v>3526.9</v>
+      </c>
+      <c r="AJ5" s="6">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="AK5" s="18"/>
-      <c r="AL5" s="19"/>
-      <c r="AM5" s="18"/>
-      <c r="AN5" s="19"/>
-      <c r="AO5" s="6" t="str">
+        <v>2240.174009</v>
+      </c>
+      <c r="AK5" s="22">
+        <v>1720.0</v>
+      </c>
+      <c r="AL5" s="21">
+        <v>0.5998</v>
+      </c>
+      <c r="AM5" s="22">
+        <v>1740.0</v>
+      </c>
+      <c r="AN5" s="21">
+        <v>0.60453</v>
+      </c>
+      <c r="AO5" s="6">
         <f>IF(OR(AK5="",AL5="",AM5="",AN5=""),"",AK5+(Assumptions!$B$8-AL5)/(AN5-AL5)*(AM5-AK5))</f>
-        <v/>
-      </c>
-      <c r="AP5" s="18"/>
-      <c r="AQ5" s="19"/>
-      <c r="AR5" s="18"/>
-      <c r="AS5" s="19"/>
-      <c r="AT5" s="6" t="str">
+        <v>1720.845666</v>
+      </c>
+      <c r="AP5" s="22">
+        <v>2660.0</v>
+      </c>
+      <c r="AQ5" s="21">
+        <v>0.79937</v>
+      </c>
+      <c r="AR5" s="22">
+        <v>2680.0</v>
+      </c>
+      <c r="AS5" s="21">
+        <v>0.8032</v>
+      </c>
+      <c r="AT5" s="6">
         <f>IF(OR(AP5="",AQ5="",AR5="",AS5=""),"",AP5+(Assumptions!$B$9-AQ5)/(AS5-AQ5)*(AR5-AP5))</f>
-        <v/>
-      </c>
-      <c r="AU5" s="6" t="str">
+        <v>2663.289817</v>
+      </c>
+      <c r="AU5" s="6">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="AV5" s="16"/>
+        <v>1720.845666</v>
+      </c>
+      <c r="AV5" s="23">
+        <f t="shared" si="9"/>
+        <v>3.1846</v>
+      </c>
+      <c r="AW5" s="23">
+        <f t="shared" si="10"/>
+        <v>0.238845</v>
+      </c>
+      <c r="AX5" s="24">
+        <f t="shared" si="11"/>
+        <v>0.716535</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="5">
@@ -5217,25 +5366,25 @@
       <c r="E6" s="5">
         <v>3.0</v>
       </c>
-      <c r="F6" s="8">
+      <c r="F6" s="11">
         <v>293.15</v>
       </c>
-      <c r="G6" s="8">
+      <c r="G6" s="11">
         <v>5.0</v>
       </c>
-      <c r="H6" s="9" t="s">
+      <c r="H6" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="I6" s="9">
+      <c r="I6" s="12">
         <v>600.0</v>
       </c>
-      <c r="J6" s="9">
+      <c r="J6" s="12">
         <v>2750.0</v>
       </c>
-      <c r="K6" s="10">
+      <c r="K6" s="13">
         <v>204000.0</v>
       </c>
-      <c r="L6" s="11">
+      <c r="L6" s="14">
         <f>Assumptions!$B$6</f>
         <v>0.00016558</v>
       </c>
@@ -5255,68 +5404,119 @@
         <f t="shared" si="2"/>
         <v>3752.07</v>
       </c>
-      <c r="Q6" s="9" t="s">
+      <c r="Q6" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="R6" s="8">
-        <v>2.8</v>
-      </c>
-      <c r="S6" s="10">
-        <v>5.0E-11</v>
-      </c>
-      <c r="T6" s="17"/>
-      <c r="U6" s="17"/>
-      <c r="V6" s="17"/>
-      <c r="W6" s="13" t="str">
+      <c r="R6" s="15">
+        <v>2.77</v>
+      </c>
+      <c r="S6" s="16">
+        <v>2.0E-11</v>
+      </c>
+      <c r="T6" s="17">
+        <v>1.6565E-5</v>
+      </c>
+      <c r="U6" s="25">
+        <v>1.4339E-6</v>
+      </c>
+      <c r="V6" s="17">
+        <v>5.6358E-4</v>
+      </c>
+      <c r="W6" s="26">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="X6" s="13" t="str">
+        <v>0.56358</v>
+      </c>
+      <c r="X6" s="26">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="Y6" s="17"/>
-      <c r="Z6" s="6" t="str">
+        <v>0.08656202837</v>
+      </c>
+      <c r="Y6" s="25">
+        <v>3040.2</v>
+      </c>
+      <c r="Z6" s="6">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="AA6" s="18"/>
-      <c r="AB6" s="17"/>
-      <c r="AC6" s="18"/>
-      <c r="AD6" s="17"/>
-      <c r="AE6" s="6" t="str">
+        <v>1.510441176</v>
+      </c>
+      <c r="AA6" s="22">
+        <v>1560.0</v>
+      </c>
+      <c r="AB6" s="25">
+        <v>2713.0</v>
+      </c>
+      <c r="AC6" s="22">
+        <v>1580.0</v>
+      </c>
+      <c r="AD6" s="25">
+        <v>2740.9</v>
+      </c>
+      <c r="AE6" s="6">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="AF6" s="18"/>
-      <c r="AG6" s="17"/>
-      <c r="AH6" s="18"/>
-      <c r="AI6" s="17"/>
-      <c r="AJ6" s="6" t="str">
+        <v>1573.670251</v>
+      </c>
+      <c r="AF6" s="22">
+        <v>2380.0</v>
+      </c>
+      <c r="AG6" s="25">
+        <v>3748.8</v>
+      </c>
+      <c r="AH6" s="22">
+        <v>2400.0</v>
+      </c>
+      <c r="AI6" s="25">
+        <v>3771.5</v>
+      </c>
+      <c r="AJ6" s="6">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="AK6" s="18"/>
-      <c r="AL6" s="19"/>
-      <c r="AM6" s="18"/>
-      <c r="AN6" s="19"/>
-      <c r="AO6" s="6" t="str">
+        <v>2382.881057</v>
+      </c>
+      <c r="AK6" s="22">
+        <v>2240.0</v>
+      </c>
+      <c r="AL6" s="21">
+        <v>0.59916</v>
+      </c>
+      <c r="AM6" s="22">
+        <v>2260.0</v>
+      </c>
+      <c r="AN6" s="21">
+        <v>0.60073</v>
+      </c>
+      <c r="AO6" s="6">
         <f>IF(OR(AK6="",AL6="",AM6="",AN6=""),"",AK6+(Assumptions!$B$8-AL6)/(AN6-AL6)*(AM6-AK6))</f>
-        <v/>
-      </c>
-      <c r="AP6" s="18"/>
-      <c r="AQ6" s="19"/>
-      <c r="AR6" s="18"/>
-      <c r="AS6" s="19"/>
-      <c r="AT6" s="6" t="str">
+        <v>2250.700637</v>
+      </c>
+      <c r="AP6" s="22">
+        <v>5060.0</v>
+      </c>
+      <c r="AQ6" s="21">
+        <v>0.79896</v>
+      </c>
+      <c r="AR6" s="22">
+        <v>5080.0</v>
+      </c>
+      <c r="AS6" s="21">
+        <v>0.80024</v>
+      </c>
+      <c r="AT6" s="6">
         <f>IF(OR(AP6="",AQ6="",AR6="",AS6=""),"",AP6+(Assumptions!$B$9-AQ6)/(AS6-AQ6)*(AR6-AP6))</f>
-        <v/>
-      </c>
-      <c r="AU6" s="6" t="str">
+        <v>5076.25</v>
+      </c>
+      <c r="AU6" s="6">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="AV6" s="16"/>
+        <v>2250.700637</v>
+      </c>
+      <c r="AV6" s="23">
+        <f t="shared" si="9"/>
+        <v>3.313</v>
+      </c>
+      <c r="AW6" s="23">
+        <f t="shared" si="10"/>
+        <v>0.248475</v>
+      </c>
+      <c r="AX6" s="24">
+        <f t="shared" si="11"/>
+        <v>0.745425</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="5">
@@ -5334,25 +5534,25 @@
       <c r="E7" s="5">
         <v>2.0</v>
       </c>
-      <c r="F7" s="8">
+      <c r="F7" s="11">
         <v>293.15</v>
       </c>
-      <c r="G7" s="8">
+      <c r="G7" s="11">
         <v>8.0</v>
       </c>
-      <c r="H7" s="9" t="s">
+      <c r="H7" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="I7" s="9">
+      <c r="I7" s="12">
         <v>500.0</v>
       </c>
-      <c r="J7" s="9">
+      <c r="J7" s="12">
         <v>2750.0</v>
       </c>
-      <c r="K7" s="10">
+      <c r="K7" s="13">
         <v>186000.0</v>
       </c>
-      <c r="L7" s="11">
+      <c r="L7" s="14">
         <f>Assumptions!$B$6</f>
         <v>0.00016558</v>
       </c>
@@ -5372,68 +5572,119 @@
         <f t="shared" si="2"/>
         <v>3206.725</v>
       </c>
-      <c r="Q7" s="9" t="s">
+      <c r="Q7" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="R7" s="8">
-        <v>2.7</v>
-      </c>
-      <c r="S7" s="10">
-        <v>1.0E-10</v>
-      </c>
-      <c r="T7" s="17"/>
-      <c r="U7" s="17"/>
-      <c r="V7" s="17"/>
-      <c r="W7" s="13" t="str">
+      <c r="R7" s="15">
+        <v>2.68</v>
+      </c>
+      <c r="S7" s="16">
+        <v>2.0E-11</v>
+      </c>
+      <c r="T7" s="17">
+        <v>1.5923E-5</v>
+      </c>
+      <c r="U7" s="25">
+        <v>1.3825E-6</v>
+      </c>
+      <c r="V7" s="17">
+        <v>6.0844E-4</v>
+      </c>
+      <c r="W7" s="26">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="X7" s="13" t="str">
+        <v>0.60844</v>
+      </c>
+      <c r="X7" s="26">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="Y7" s="17"/>
-      <c r="Z7" s="6" t="str">
+        <v>0.08682409094</v>
+      </c>
+      <c r="Y7" s="25">
+        <v>3824.0</v>
+      </c>
+      <c r="Z7" s="6">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="AA7" s="18"/>
-      <c r="AB7" s="17"/>
-      <c r="AC7" s="18"/>
-      <c r="AD7" s="17"/>
-      <c r="AE7" s="6" t="str">
+        <v>8.318682796</v>
+      </c>
+      <c r="AA7" s="22">
+        <v>880.0</v>
+      </c>
+      <c r="AB7" s="25">
+        <v>2253.6</v>
+      </c>
+      <c r="AC7" s="22">
+        <v>900.0</v>
+      </c>
+      <c r="AD7" s="25">
+        <v>2293.6</v>
+      </c>
+      <c r="AE7" s="6">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="AF7" s="18"/>
-      <c r="AG7" s="17"/>
-      <c r="AH7" s="18"/>
-      <c r="AI7" s="17"/>
-      <c r="AJ7" s="6" t="str">
+        <v>891.5625</v>
+      </c>
+      <c r="AF7" s="22">
+        <v>1380.0</v>
+      </c>
+      <c r="AG7" s="25">
+        <v>3178.0</v>
+      </c>
+      <c r="AH7" s="22">
+        <v>1400.0</v>
+      </c>
+      <c r="AI7" s="25">
+        <v>3211.9</v>
+      </c>
+      <c r="AJ7" s="6">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="AK7" s="18"/>
-      <c r="AL7" s="19"/>
-      <c r="AM7" s="18"/>
-      <c r="AN7" s="19"/>
-      <c r="AO7" s="6" t="str">
+        <v>1396.946903</v>
+      </c>
+      <c r="AK7" s="22">
+        <v>1680.0</v>
+      </c>
+      <c r="AL7" s="21">
+        <v>0.59902</v>
+      </c>
+      <c r="AM7" s="22">
+        <v>1700.0</v>
+      </c>
+      <c r="AN7" s="21">
+        <v>0.60061</v>
+      </c>
+      <c r="AO7" s="6">
         <f>IF(OR(AK7="",AL7="",AM7="",AN7=""),"",AK7+(Assumptions!$B$8-AL7)/(AN7-AL7)*(AM7-AK7))</f>
-        <v/>
-      </c>
-      <c r="AP7" s="18"/>
-      <c r="AQ7" s="19"/>
-      <c r="AR7" s="18"/>
-      <c r="AS7" s="19"/>
-      <c r="AT7" s="6" t="str">
+        <v>1692.327044</v>
+      </c>
+      <c r="AP7" s="22">
+        <v>4520.0</v>
+      </c>
+      <c r="AQ7" s="21">
+        <v>0.79989</v>
+      </c>
+      <c r="AR7" s="22">
+        <v>4540.0</v>
+      </c>
+      <c r="AS7" s="21">
+        <v>0.80117</v>
+      </c>
+      <c r="AT7" s="6">
         <f>IF(OR(AP7="",AQ7="",AR7="",AS7=""),"",AP7+(Assumptions!$B$9-AQ7)/(AS7-AQ7)*(AR7-AP7))</f>
-        <v/>
-      </c>
-      <c r="AU7" s="6" t="str">
+        <v>4521.71875</v>
+      </c>
+      <c r="AU7" s="6">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="AV7" s="16"/>
+        <v>1396.946903</v>
+      </c>
+      <c r="AV7" s="23">
+        <f t="shared" si="9"/>
+        <v>3.1846</v>
+      </c>
+      <c r="AW7" s="23">
+        <f t="shared" si="10"/>
+        <v>0.238845</v>
+      </c>
+      <c r="AX7" s="24">
+        <f t="shared" si="11"/>
+        <v>0.716535</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="5">
@@ -5451,25 +5702,25 @@
       <c r="E8" s="5">
         <v>3.0</v>
       </c>
-      <c r="F8" s="8">
+      <c r="F8" s="11">
         <v>293.15</v>
       </c>
-      <c r="G8" s="8">
+      <c r="G8" s="11">
         <v>8.0</v>
       </c>
-      <c r="H8" s="9" t="s">
+      <c r="H8" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="I8" s="9">
+      <c r="I8" s="12">
         <v>550.0</v>
       </c>
-      <c r="J8" s="9">
+      <c r="J8" s="12">
         <v>2750.0</v>
       </c>
-      <c r="K8" s="10">
+      <c r="K8" s="13">
         <v>200000.0</v>
       </c>
-      <c r="L8" s="11">
+      <c r="L8" s="14">
         <f>Assumptions!$B$6</f>
         <v>0.00016558</v>
       </c>
@@ -5489,68 +5740,119 @@
         <f t="shared" si="2"/>
         <v>3504.3975</v>
       </c>
-      <c r="Q8" s="9" t="s">
+      <c r="Q8" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="R8" s="8">
-        <v>2.8</v>
-      </c>
-      <c r="S8" s="10">
-        <v>5.0E-11</v>
-      </c>
-      <c r="T8" s="17"/>
-      <c r="U8" s="17"/>
-      <c r="V8" s="17"/>
-      <c r="W8" s="13" t="str">
+      <c r="R8" s="15">
+        <v>2.77</v>
+      </c>
+      <c r="S8" s="16">
+        <v>5.0E-12</v>
+      </c>
+      <c r="T8" s="17">
+        <v>1.6565E-5</v>
+      </c>
+      <c r="U8" s="25">
+        <v>1.4091E-6</v>
+      </c>
+      <c r="V8" s="17">
+        <v>5.622E-4</v>
+      </c>
+      <c r="W8" s="26">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="X8" s="13" t="str">
+        <v>0.5622</v>
+      </c>
+      <c r="X8" s="26">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="Y8" s="17"/>
-      <c r="Z8" s="6" t="str">
+        <v>0.08506489586</v>
+      </c>
+      <c r="Y8" s="25">
+        <v>3937.4</v>
+      </c>
+      <c r="Z8" s="6">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="AA8" s="18"/>
-      <c r="AB8" s="17"/>
-      <c r="AC8" s="18"/>
-      <c r="AD8" s="17"/>
-      <c r="AE8" s="6" t="str">
+        <v>7.1650125</v>
+      </c>
+      <c r="AA8" s="22">
+        <v>960.0</v>
+      </c>
+      <c r="AB8" s="25">
+        <v>2500.2</v>
+      </c>
+      <c r="AC8" s="22">
+        <v>980.0</v>
+      </c>
+      <c r="AD8" s="25">
+        <v>2542.4</v>
+      </c>
+      <c r="AE8" s="6">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="AF8" s="18"/>
-      <c r="AG8" s="17"/>
-      <c r="AH8" s="18"/>
-      <c r="AI8" s="17"/>
-      <c r="AJ8" s="6" t="str">
+        <v>961.9893365</v>
+      </c>
+      <c r="AF8" s="22">
+        <v>1500.0</v>
+      </c>
+      <c r="AG8" s="25">
+        <v>3486.1</v>
+      </c>
+      <c r="AH8" s="22">
+        <v>1520.0</v>
+      </c>
+      <c r="AI8" s="25">
+        <v>3518.0</v>
+      </c>
+      <c r="AJ8" s="6">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="AK8" s="18"/>
-      <c r="AL8" s="19"/>
-      <c r="AM8" s="18"/>
-      <c r="AN8" s="19"/>
-      <c r="AO8" s="6" t="str">
+        <v>1511.471787</v>
+      </c>
+      <c r="AK8" s="22">
+        <v>3660.0</v>
+      </c>
+      <c r="AL8" s="21">
+        <v>0.59978</v>
+      </c>
+      <c r="AM8" s="22">
+        <v>3680.0</v>
+      </c>
+      <c r="AN8" s="21">
+        <v>0.60018</v>
+      </c>
+      <c r="AO8" s="6">
         <f>IF(OR(AK8="",AL8="",AM8="",AN8=""),"",AK8+(Assumptions!$B$8-AL8)/(AN8-AL8)*(AM8-AK8))</f>
-        <v/>
-      </c>
-      <c r="AP8" s="18"/>
-      <c r="AQ8" s="19"/>
-      <c r="AR8" s="18"/>
-      <c r="AS8" s="19"/>
-      <c r="AT8" s="6" t="str">
+        <v>3671</v>
+      </c>
+      <c r="AP8" s="22">
+        <v>14980.0</v>
+      </c>
+      <c r="AQ8" s="21">
+        <v>0.79999</v>
+      </c>
+      <c r="AR8" s="22">
+        <v>15000.0</v>
+      </c>
+      <c r="AS8" s="21">
+        <v>0.80031</v>
+      </c>
+      <c r="AT8" s="6">
         <f>IF(OR(AP8="",AQ8="",AR8="",AS8=""),"",AP8+(Assumptions!$B$9-AQ8)/(AS8-AQ8)*(AR8-AP8))</f>
-        <v/>
-      </c>
-      <c r="AU8" s="6" t="str">
+        <v>14980.625</v>
+      </c>
+      <c r="AU8" s="6">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="AV8" s="16"/>
+        <v>1511.471787</v>
+      </c>
+      <c r="AV8" s="23">
+        <f t="shared" si="9"/>
+        <v>3.313</v>
+      </c>
+      <c r="AW8" s="23">
+        <f t="shared" si="10"/>
+        <v>0.248475</v>
+      </c>
+      <c r="AX8" s="24">
+        <f t="shared" si="11"/>
+        <v>0.745425</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="5">
@@ -5568,25 +5870,25 @@
       <c r="E9" s="5">
         <v>1.0</v>
       </c>
-      <c r="F9" s="8">
+      <c r="F9" s="11">
         <v>293.15</v>
       </c>
-      <c r="G9" s="8">
+      <c r="G9" s="11">
         <v>8.0</v>
       </c>
-      <c r="H9" s="9" t="s">
+      <c r="H9" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="I9" s="9">
+      <c r="I9" s="12">
         <v>600.0</v>
       </c>
-      <c r="J9" s="9">
+      <c r="J9" s="12">
         <v>2750.0</v>
       </c>
-      <c r="K9" s="10">
+      <c r="K9" s="13">
         <v>204000.0</v>
       </c>
-      <c r="L9" s="11">
+      <c r="L9" s="14">
         <f>Assumptions!$B$6</f>
         <v>0.00016558</v>
       </c>
@@ -5606,68 +5908,119 @@
         <f t="shared" si="2"/>
         <v>3752.07</v>
       </c>
-      <c r="Q9" s="9" t="s">
+      <c r="Q9" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="R9" s="8">
-        <v>2.6</v>
-      </c>
-      <c r="S9" s="10">
-        <v>2.0E-10</v>
-      </c>
-      <c r="T9" s="17"/>
-      <c r="U9" s="17"/>
-      <c r="V9" s="17"/>
-      <c r="W9" s="13" t="str">
+      <c r="R9" s="15">
+        <v>2.58</v>
+      </c>
+      <c r="S9" s="16">
+        <v>6.0E-11</v>
+      </c>
+      <c r="T9" s="17">
+        <v>1.5219E-5</v>
+      </c>
+      <c r="U9" s="25">
+        <v>1.7855E-6</v>
+      </c>
+      <c r="V9" s="17">
+        <v>7.7944E-4</v>
+      </c>
+      <c r="W9" s="26">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="X9" s="13" t="str">
+        <v>0.77944</v>
+      </c>
+      <c r="X9" s="26">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="Y9" s="17"/>
-      <c r="Z9" s="6" t="str">
+        <v>0.1173204547</v>
+      </c>
+      <c r="Y9" s="25">
+        <v>4146.3</v>
+      </c>
+      <c r="Z9" s="6">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="AA9" s="18"/>
-      <c r="AB9" s="17"/>
-      <c r="AC9" s="18"/>
-      <c r="AD9" s="17"/>
-      <c r="AE9" s="6" t="str">
+        <v>6.9325</v>
+      </c>
+      <c r="AA9" s="22">
+        <v>1020.0</v>
+      </c>
+      <c r="AB9" s="25">
+        <v>2698.3</v>
+      </c>
+      <c r="AC9" s="22">
+        <v>1040.0</v>
+      </c>
+      <c r="AD9" s="25">
+        <v>2741.2</v>
+      </c>
+      <c r="AE9" s="6">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="AF9" s="18"/>
-      <c r="AG9" s="17"/>
-      <c r="AH9" s="18"/>
-      <c r="AI9" s="17"/>
-      <c r="AJ9" s="6" t="str">
+        <v>1035.74359</v>
+      </c>
+      <c r="AF9" s="22">
+        <v>1560.0</v>
+      </c>
+      <c r="AG9" s="25">
+        <v>3746.4</v>
+      </c>
+      <c r="AH9" s="22">
+        <v>1580.0</v>
+      </c>
+      <c r="AI9" s="25">
+        <v>3781.2</v>
+      </c>
+      <c r="AJ9" s="6">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="AK9" s="18"/>
-      <c r="AL9" s="19"/>
-      <c r="AM9" s="18"/>
-      <c r="AN9" s="19"/>
-      <c r="AO9" s="6" t="str">
+        <v>1563.258621</v>
+      </c>
+      <c r="AK9" s="22">
+        <v>1340.0</v>
+      </c>
+      <c r="AL9" s="21">
+        <v>0.59064</v>
+      </c>
+      <c r="AM9" s="22">
+        <v>1360.0</v>
+      </c>
+      <c r="AN9" s="21">
+        <v>0.60016</v>
+      </c>
+      <c r="AO9" s="6">
         <f>IF(OR(AK9="",AL9="",AM9="",AN9=""),"",AK9+(Assumptions!$B$8-AL9)/(AN9-AL9)*(AM9-AK9))</f>
-        <v/>
-      </c>
-      <c r="AP9" s="18"/>
-      <c r="AQ9" s="19"/>
-      <c r="AR9" s="18"/>
-      <c r="AS9" s="19"/>
-      <c r="AT9" s="6" t="str">
+        <v>1359.663866</v>
+      </c>
+      <c r="AP9" s="22">
+        <v>2300.0</v>
+      </c>
+      <c r="AQ9" s="21">
+        <v>0.79937</v>
+      </c>
+      <c r="AR9" s="22">
+        <v>2320.0</v>
+      </c>
+      <c r="AS9" s="21">
+        <v>0.8032</v>
+      </c>
+      <c r="AT9" s="6">
         <f>IF(OR(AP9="",AQ9="",AR9="",AS9=""),"",AP9+(Assumptions!$B$9-AQ9)/(AS9-AQ9)*(AR9-AP9))</f>
-        <v/>
-      </c>
-      <c r="AU9" s="6" t="str">
+        <v>2303.289817</v>
+      </c>
+      <c r="AU9" s="6">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="AV9" s="16"/>
+        <v>1359.663866</v>
+      </c>
+      <c r="AV9" s="23">
+        <f t="shared" si="9"/>
+        <v>3.0438</v>
+      </c>
+      <c r="AW9" s="23">
+        <f t="shared" si="10"/>
+        <v>0.228285</v>
+      </c>
+      <c r="AX9" s="24">
+        <f t="shared" si="11"/>
+        <v>0.684855</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="5">
@@ -5685,25 +6038,25 @@
       <c r="E10" s="5">
         <v>3.0</v>
       </c>
-      <c r="F10" s="8">
+      <c r="F10" s="11">
         <v>293.15</v>
       </c>
-      <c r="G10" s="8">
+      <c r="G10" s="11">
         <v>12.0</v>
       </c>
-      <c r="H10" s="9" t="s">
+      <c r="H10" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="I10" s="9">
+      <c r="I10" s="12">
         <v>500.0</v>
       </c>
-      <c r="J10" s="9">
+      <c r="J10" s="12">
         <v>2750.0</v>
       </c>
-      <c r="K10" s="10">
+      <c r="K10" s="13">
         <v>186000.0</v>
       </c>
-      <c r="L10" s="11">
+      <c r="L10" s="14">
         <f>Assumptions!$B$6</f>
         <v>0.00016558</v>
       </c>
@@ -5723,68 +6076,119 @@
         <f t="shared" si="2"/>
         <v>3206.725</v>
       </c>
-      <c r="Q10" s="9" t="s">
+      <c r="Q10" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="R10" s="8">
-        <v>2.8</v>
-      </c>
-      <c r="S10" s="10">
-        <v>5.0E-11</v>
-      </c>
-      <c r="T10" s="17"/>
-      <c r="U10" s="17"/>
-      <c r="V10" s="17"/>
-      <c r="W10" s="13" t="str">
+      <c r="R10" s="15">
+        <v>2.77</v>
+      </c>
+      <c r="S10" s="16">
+        <v>6.0E-11</v>
+      </c>
+      <c r="T10" s="17">
+        <v>1.6565E-5</v>
+      </c>
+      <c r="U10" s="25">
+        <v>1.7996E-6</v>
+      </c>
+      <c r="V10" s="17">
+        <v>7.9904E-4</v>
+      </c>
+      <c r="W10" s="26">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="X10" s="13" t="str">
+        <v>0.79904</v>
+      </c>
+      <c r="X10" s="26">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="Y10" s="17"/>
-      <c r="Z10" s="6" t="str">
+        <v>0.108638696</v>
+      </c>
+      <c r="Y10" s="25">
+        <v>4674.8</v>
+      </c>
+      <c r="Z10" s="6">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="AA10" s="18"/>
-      <c r="AB10" s="17"/>
-      <c r="AC10" s="18"/>
-      <c r="AD10" s="17"/>
-      <c r="AE10" s="6" t="str">
+        <v>12.89287634</v>
+      </c>
+      <c r="AA10" s="22">
+        <v>620.0</v>
+      </c>
+      <c r="AB10" s="25">
+        <v>2224.3</v>
+      </c>
+      <c r="AC10" s="22">
+        <v>640.0</v>
+      </c>
+      <c r="AD10" s="25">
+        <v>2280.7</v>
+      </c>
+      <c r="AE10" s="6">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="AF10" s="18"/>
-      <c r="AG10" s="17"/>
-      <c r="AH10" s="18"/>
-      <c r="AI10" s="17"/>
-      <c r="AJ10" s="6" t="str">
+        <v>638.5904255</v>
+      </c>
+      <c r="AF10" s="22">
+        <v>980.0</v>
+      </c>
+      <c r="AG10" s="25">
+        <v>3180.4</v>
+      </c>
+      <c r="AH10" s="22">
+        <v>1000.0</v>
+      </c>
+      <c r="AI10" s="25">
+        <v>3227.2</v>
+      </c>
+      <c r="AJ10" s="6">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="AK10" s="18"/>
-      <c r="AL10" s="19"/>
-      <c r="AM10" s="18"/>
-      <c r="AN10" s="19"/>
-      <c r="AO10" s="6" t="str">
+        <v>991.25</v>
+      </c>
+      <c r="AK10" s="22">
+        <v>860.0</v>
+      </c>
+      <c r="AL10" s="21">
+        <v>0.59905</v>
+      </c>
+      <c r="AM10" s="22">
+        <v>880.0</v>
+      </c>
+      <c r="AN10" s="21">
+        <v>0.60381</v>
+      </c>
+      <c r="AO10" s="6">
         <f>IF(OR(AK10="",AL10="",AM10="",AN10=""),"",AK10+(Assumptions!$B$8-AL10)/(AN10-AL10)*(AM10-AK10))</f>
-        <v/>
-      </c>
-      <c r="AP10" s="18"/>
-      <c r="AQ10" s="19"/>
-      <c r="AR10" s="18"/>
-      <c r="AS10" s="19"/>
-      <c r="AT10" s="6" t="str">
+        <v>863.9915966</v>
+      </c>
+      <c r="AP10" s="22">
+        <v>1800.0</v>
+      </c>
+      <c r="AQ10" s="21">
+        <v>0.79903</v>
+      </c>
+      <c r="AR10" s="22">
+        <v>1820.0</v>
+      </c>
+      <c r="AS10" s="21">
+        <v>0.80286</v>
+      </c>
+      <c r="AT10" s="6">
         <f>IF(OR(AP10="",AQ10="",AR10="",AS10=""),"",AP10+(Assumptions!$B$9-AQ10)/(AS10-AQ10)*(AR10-AP10))</f>
-        <v/>
-      </c>
-      <c r="AU10" s="6" t="str">
+        <v>1805.065274</v>
+      </c>
+      <c r="AU10" s="6">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="AV10" s="16"/>
+        <v>863.9915966</v>
+      </c>
+      <c r="AV10" s="23">
+        <f t="shared" si="9"/>
+        <v>3.313</v>
+      </c>
+      <c r="AW10" s="23">
+        <f t="shared" si="10"/>
+        <v>0.248475</v>
+      </c>
+      <c r="AX10" s="24">
+        <f t="shared" si="11"/>
+        <v>0.745425</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="5">
@@ -5802,25 +6206,25 @@
       <c r="E11" s="5">
         <v>1.0</v>
       </c>
-      <c r="F11" s="8">
+      <c r="F11" s="11">
         <v>293.15</v>
       </c>
-      <c r="G11" s="8">
+      <c r="G11" s="11">
         <v>12.0</v>
       </c>
-      <c r="H11" s="9" t="s">
+      <c r="H11" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="I11" s="9">
+      <c r="I11" s="12">
         <v>550.0</v>
       </c>
-      <c r="J11" s="9">
+      <c r="J11" s="12">
         <v>2750.0</v>
       </c>
-      <c r="K11" s="10">
+      <c r="K11" s="13">
         <v>200000.0</v>
       </c>
-      <c r="L11" s="11">
+      <c r="L11" s="14">
         <f>Assumptions!$B$6</f>
         <v>0.00016558</v>
       </c>
@@ -5840,68 +6244,119 @@
         <f t="shared" si="2"/>
         <v>3504.3975</v>
       </c>
-      <c r="Q11" s="9" t="s">
+      <c r="Q11" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="R11" s="8">
-        <v>2.6</v>
-      </c>
-      <c r="S11" s="10">
-        <v>2.0E-10</v>
-      </c>
-      <c r="T11" s="17"/>
-      <c r="U11" s="17"/>
-      <c r="V11" s="17"/>
-      <c r="W11" s="13" t="str">
+      <c r="R11" s="15">
+        <v>2.58</v>
+      </c>
+      <c r="S11" s="16">
+        <v>2.0E-11</v>
+      </c>
+      <c r="T11" s="17">
+        <v>1.5219E-5</v>
+      </c>
+      <c r="U11" s="25">
+        <v>1.5379E-6</v>
+      </c>
+      <c r="V11" s="25">
+        <v>6.1192E-4</v>
+      </c>
+      <c r="W11" s="26">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="X11" s="13" t="str">
+        <v>0.61192</v>
+      </c>
+      <c r="X11" s="26">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="Y11" s="17"/>
-      <c r="Z11" s="6" t="str">
+        <v>0.1010513174</v>
+      </c>
+      <c r="Y11" s="25">
+        <v>4927.2</v>
+      </c>
+      <c r="Z11" s="6">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="AA11" s="18"/>
-      <c r="AB11" s="17"/>
-      <c r="AC11" s="18"/>
-      <c r="AD11" s="17"/>
-      <c r="AE11" s="6" t="str">
+        <v>12.1140125</v>
+      </c>
+      <c r="AA11" s="22">
+        <v>660.0</v>
+      </c>
+      <c r="AB11" s="25">
+        <v>2455.4</v>
+      </c>
+      <c r="AC11" s="22">
+        <v>680.0</v>
+      </c>
+      <c r="AD11" s="25">
+        <v>2515.2</v>
+      </c>
+      <c r="AE11" s="6">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="AF11" s="18"/>
-      <c r="AG11" s="17"/>
-      <c r="AH11" s="18"/>
-      <c r="AI11" s="17"/>
-      <c r="AJ11" s="6" t="str">
+        <v>676.3871237</v>
+      </c>
+      <c r="AF11" s="22">
+        <v>1040.0</v>
+      </c>
+      <c r="AG11" s="25">
+        <v>3457.2</v>
+      </c>
+      <c r="AH11" s="22">
+        <v>1060.0</v>
+      </c>
+      <c r="AI11" s="25">
+        <v>3504.9</v>
+      </c>
+      <c r="AJ11" s="6">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="AK11" s="18"/>
-      <c r="AL11" s="19"/>
-      <c r="AM11" s="18"/>
-      <c r="AN11" s="19"/>
-      <c r="AO11" s="6" t="str">
+        <v>1059.789308</v>
+      </c>
+      <c r="AK11" s="22">
+        <v>2020.0</v>
+      </c>
+      <c r="AL11" s="21">
+        <v>0.59941</v>
+      </c>
+      <c r="AM11" s="22">
+        <v>2040.0</v>
+      </c>
+      <c r="AN11" s="21">
+        <v>0.60099</v>
+      </c>
+      <c r="AO11" s="6">
         <f>IF(OR(AK11="",AL11="",AM11="",AN11=""),"",AK11+(Assumptions!$B$8-AL11)/(AN11-AL11)*(AM11-AK11))</f>
-        <v/>
-      </c>
-      <c r="AP11" s="18"/>
-      <c r="AQ11" s="19"/>
-      <c r="AR11" s="18"/>
-      <c r="AS11" s="19"/>
-      <c r="AT11" s="6" t="str">
+        <v>2027.468354</v>
+      </c>
+      <c r="AP11" s="22">
+        <v>4860.0</v>
+      </c>
+      <c r="AQ11" s="21">
+        <v>0.79997</v>
+      </c>
+      <c r="AR11" s="22">
+        <v>4880.0</v>
+      </c>
+      <c r="AS11" s="21">
+        <v>0.80125</v>
+      </c>
+      <c r="AT11" s="6">
         <f>IF(OR(AP11="",AQ11="",AR11="",AS11=""),"",AP11+(Assumptions!$B$9-AQ11)/(AS11-AQ11)*(AR11-AP11))</f>
-        <v/>
-      </c>
-      <c r="AU11" s="6" t="str">
+        <v>4860.46875</v>
+      </c>
+      <c r="AU11" s="6">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="AV11" s="16"/>
+        <v>1059.789308</v>
+      </c>
+      <c r="AV11" s="23">
+        <f t="shared" si="9"/>
+        <v>3.0438</v>
+      </c>
+      <c r="AW11" s="23">
+        <f t="shared" si="10"/>
+        <v>0.228285</v>
+      </c>
+      <c r="AX11" s="24">
+        <f t="shared" si="11"/>
+        <v>0.684855</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="5">
@@ -5919,25 +6374,25 @@
       <c r="E12" s="5">
         <v>2.0</v>
       </c>
-      <c r="F12" s="8">
+      <c r="F12" s="11">
         <v>293.15</v>
       </c>
-      <c r="G12" s="8">
+      <c r="G12" s="11">
         <v>12.0</v>
       </c>
-      <c r="H12" s="9" t="s">
+      <c r="H12" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="I12" s="9">
+      <c r="I12" s="12">
         <v>600.0</v>
       </c>
-      <c r="J12" s="9">
+      <c r="J12" s="12">
         <v>2750.0</v>
       </c>
-      <c r="K12" s="10">
+      <c r="K12" s="13">
         <v>204000.0</v>
       </c>
-      <c r="L12" s="11">
+      <c r="L12" s="14">
         <f>Assumptions!$B$6</f>
         <v>0.00016558</v>
       </c>
@@ -5957,59 +6412,59 @@
         <f t="shared" si="2"/>
         <v>3752.07</v>
       </c>
-      <c r="Q12" s="9" t="s">
+      <c r="Q12" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="R12" s="8">
-        <v>2.7</v>
-      </c>
-      <c r="S12" s="10">
-        <v>1.0E-10</v>
-      </c>
-      <c r="T12" s="17"/>
-      <c r="U12" s="17"/>
-      <c r="V12" s="17"/>
-      <c r="W12" s="13" t="str">
+      <c r="R12" s="15">
+        <v>2.68</v>
+      </c>
+      <c r="S12" s="16">
+        <v>5.0E-12</v>
+      </c>
+      <c r="T12" s="27"/>
+      <c r="U12" s="27"/>
+      <c r="V12" s="27"/>
+      <c r="W12" s="26" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="X12" s="13" t="str">
+      <c r="X12" s="26" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="Y12" s="17"/>
+      <c r="Y12" s="27"/>
       <c r="Z12" s="6" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="AA12" s="18"/>
-      <c r="AB12" s="17"/>
-      <c r="AC12" s="18"/>
-      <c r="AD12" s="17"/>
+      <c r="AA12" s="28"/>
+      <c r="AB12" s="27"/>
+      <c r="AC12" s="28"/>
+      <c r="AD12" s="27"/>
       <c r="AE12" s="6" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="AF12" s="18"/>
-      <c r="AG12" s="17"/>
-      <c r="AH12" s="18"/>
-      <c r="AI12" s="17"/>
+      <c r="AF12" s="28"/>
+      <c r="AG12" s="27"/>
+      <c r="AH12" s="28"/>
+      <c r="AI12" s="27"/>
       <c r="AJ12" s="6" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="AK12" s="18"/>
-      <c r="AL12" s="19"/>
-      <c r="AM12" s="18"/>
-      <c r="AN12" s="19"/>
+      <c r="AK12" s="28"/>
+      <c r="AL12" s="29"/>
+      <c r="AM12" s="28"/>
+      <c r="AN12" s="29"/>
       <c r="AO12" s="6" t="str">
         <f>IF(OR(AK12="",AL12="",AM12="",AN12=""),"",AK12+(Assumptions!$B$8-AL12)/(AN12-AL12)*(AM12-AK12))</f>
         <v/>
       </c>
-      <c r="AP12" s="18"/>
-      <c r="AQ12" s="19"/>
-      <c r="AR12" s="18"/>
-      <c r="AS12" s="19"/>
+      <c r="AP12" s="28"/>
+      <c r="AQ12" s="29"/>
+      <c r="AR12" s="28"/>
+      <c r="AS12" s="29"/>
       <c r="AT12" s="6" t="str">
         <f>IF(OR(AP12="",AQ12="",AR12="",AS12=""),"",AP12+(Assumptions!$B$9-AQ12)/(AS12-AQ12)*(AR12-AP12))</f>
         <v/>
@@ -6018,7 +6473,18 @@
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="AV12" s="16"/>
+      <c r="AV12" s="23">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AW12" s="23">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="AX12" s="24">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="5">
@@ -6036,25 +6502,25 @@
       <c r="E13" s="5">
         <v>2.0</v>
       </c>
-      <c r="F13" s="8">
+      <c r="F13" s="11">
         <v>298.15</v>
       </c>
-      <c r="G13" s="8">
+      <c r="G13" s="11">
         <v>5.0</v>
       </c>
-      <c r="H13" s="9" t="s">
+      <c r="H13" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="I13" s="9">
+      <c r="I13" s="12">
         <v>500.0</v>
       </c>
-      <c r="J13" s="9">
+      <c r="J13" s="12">
         <v>2750.0</v>
       </c>
-      <c r="K13" s="10">
+      <c r="K13" s="13">
         <v>186000.0</v>
       </c>
-      <c r="L13" s="11">
+      <c r="L13" s="14">
         <f>Assumptions!$B$6</f>
         <v>0.00016558</v>
       </c>
@@ -6074,59 +6540,59 @@
         <f t="shared" si="2"/>
         <v>3206.725</v>
       </c>
-      <c r="Q13" s="9" t="s">
+      <c r="Q13" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="R13" s="8">
-        <v>2.7</v>
-      </c>
-      <c r="S13" s="10">
-        <v>1.0E-10</v>
-      </c>
-      <c r="T13" s="17"/>
-      <c r="U13" s="17"/>
-      <c r="V13" s="17"/>
-      <c r="W13" s="13" t="str">
+      <c r="R13" s="15">
+        <v>2.68</v>
+      </c>
+      <c r="S13" s="16">
+        <v>2.0E-11</v>
+      </c>
+      <c r="T13" s="27"/>
+      <c r="U13" s="27"/>
+      <c r="V13" s="27"/>
+      <c r="W13" s="26" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="X13" s="13" t="str">
+      <c r="X13" s="26" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="Y13" s="17"/>
+      <c r="Y13" s="27"/>
       <c r="Z13" s="6" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="AA13" s="18"/>
-      <c r="AB13" s="17"/>
-      <c r="AC13" s="18"/>
-      <c r="AD13" s="17"/>
+      <c r="AA13" s="28"/>
+      <c r="AB13" s="27"/>
+      <c r="AC13" s="28"/>
+      <c r="AD13" s="27"/>
       <c r="AE13" s="6" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="AF13" s="18"/>
-      <c r="AG13" s="17"/>
-      <c r="AH13" s="18"/>
-      <c r="AI13" s="17"/>
+      <c r="AF13" s="28"/>
+      <c r="AG13" s="27"/>
+      <c r="AH13" s="28"/>
+      <c r="AI13" s="27"/>
       <c r="AJ13" s="6" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="AK13" s="18"/>
-      <c r="AL13" s="19"/>
-      <c r="AM13" s="18"/>
-      <c r="AN13" s="19"/>
+      <c r="AK13" s="28"/>
+      <c r="AL13" s="29"/>
+      <c r="AM13" s="28"/>
+      <c r="AN13" s="29"/>
       <c r="AO13" s="6" t="str">
         <f>IF(OR(AK13="",AL13="",AM13="",AN13=""),"",AK13+(Assumptions!$B$8-AL13)/(AN13-AL13)*(AM13-AK13))</f>
         <v/>
       </c>
-      <c r="AP13" s="18"/>
-      <c r="AQ13" s="19"/>
-      <c r="AR13" s="18"/>
-      <c r="AS13" s="19"/>
+      <c r="AP13" s="28"/>
+      <c r="AQ13" s="29"/>
+      <c r="AR13" s="28"/>
+      <c r="AS13" s="29"/>
       <c r="AT13" s="6" t="str">
         <f>IF(OR(AP13="",AQ13="",AR13="",AS13=""),"",AP13+(Assumptions!$B$9-AQ13)/(AS13-AQ13)*(AR13-AP13))</f>
         <v/>
@@ -6135,7 +6601,18 @@
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="AV13" s="16"/>
+      <c r="AV13" s="23">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AW13" s="23">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="AX13" s="24">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="5">
@@ -6153,25 +6630,25 @@
       <c r="E14" s="5">
         <v>3.0</v>
       </c>
-      <c r="F14" s="8">
+      <c r="F14" s="11">
         <v>298.15</v>
       </c>
-      <c r="G14" s="8">
+      <c r="G14" s="11">
         <v>5.0</v>
       </c>
-      <c r="H14" s="9" t="s">
+      <c r="H14" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="I14" s="9">
+      <c r="I14" s="12">
         <v>550.0</v>
       </c>
-      <c r="J14" s="9">
+      <c r="J14" s="12">
         <v>2750.0</v>
       </c>
-      <c r="K14" s="10">
+      <c r="K14" s="13">
         <v>200000.0</v>
       </c>
-      <c r="L14" s="11">
+      <c r="L14" s="14">
         <f>Assumptions!$B$6</f>
         <v>0.00016558</v>
       </c>
@@ -6191,59 +6668,59 @@
         <f t="shared" si="2"/>
         <v>3504.3975</v>
       </c>
-      <c r="Q14" s="9" t="s">
+      <c r="Q14" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="R14" s="8">
-        <v>2.8</v>
-      </c>
-      <c r="S14" s="10">
-        <v>5.0E-11</v>
-      </c>
-      <c r="T14" s="17"/>
-      <c r="U14" s="17"/>
-      <c r="V14" s="17"/>
-      <c r="W14" s="13" t="str">
+      <c r="R14" s="15">
+        <v>2.77</v>
+      </c>
+      <c r="S14" s="16">
+        <v>5.0E-12</v>
+      </c>
+      <c r="T14" s="27"/>
+      <c r="U14" s="27"/>
+      <c r="V14" s="27"/>
+      <c r="W14" s="26" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="X14" s="13" t="str">
+      <c r="X14" s="26" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="Y14" s="17"/>
+      <c r="Y14" s="27"/>
       <c r="Z14" s="6" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="AA14" s="18"/>
-      <c r="AB14" s="17"/>
-      <c r="AC14" s="18"/>
-      <c r="AD14" s="17"/>
+      <c r="AA14" s="28"/>
+      <c r="AB14" s="27"/>
+      <c r="AC14" s="28"/>
+      <c r="AD14" s="27"/>
       <c r="AE14" s="6" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="AF14" s="18"/>
-      <c r="AG14" s="17"/>
-      <c r="AH14" s="18"/>
-      <c r="AI14" s="17"/>
+      <c r="AF14" s="28"/>
+      <c r="AG14" s="27"/>
+      <c r="AH14" s="28"/>
+      <c r="AI14" s="27"/>
       <c r="AJ14" s="6" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="AK14" s="18"/>
-      <c r="AL14" s="19"/>
-      <c r="AM14" s="18"/>
-      <c r="AN14" s="19"/>
+      <c r="AK14" s="28"/>
+      <c r="AL14" s="29"/>
+      <c r="AM14" s="28"/>
+      <c r="AN14" s="29"/>
       <c r="AO14" s="6" t="str">
         <f>IF(OR(AK14="",AL14="",AM14="",AN14=""),"",AK14+(Assumptions!$B$8-AL14)/(AN14-AL14)*(AM14-AK14))</f>
         <v/>
       </c>
-      <c r="AP14" s="18"/>
-      <c r="AQ14" s="19"/>
-      <c r="AR14" s="18"/>
-      <c r="AS14" s="19"/>
+      <c r="AP14" s="28"/>
+      <c r="AQ14" s="29"/>
+      <c r="AR14" s="28"/>
+      <c r="AS14" s="29"/>
       <c r="AT14" s="6" t="str">
         <f>IF(OR(AP14="",AQ14="",AR14="",AS14=""),"",AP14+(Assumptions!$B$9-AQ14)/(AS14-AQ14)*(AR14-AP14))</f>
         <v/>
@@ -6252,7 +6729,18 @@
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="AV14" s="16"/>
+      <c r="AV14" s="23">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AW14" s="23">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="AX14" s="24">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="5">
@@ -6270,25 +6758,25 @@
       <c r="E15" s="5">
         <v>1.0</v>
       </c>
-      <c r="F15" s="8">
+      <c r="F15" s="11">
         <v>298.15</v>
       </c>
-      <c r="G15" s="8">
+      <c r="G15" s="11">
         <v>5.0</v>
       </c>
-      <c r="H15" s="9" t="s">
+      <c r="H15" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="I15" s="9">
+      <c r="I15" s="12">
         <v>600.0</v>
       </c>
-      <c r="J15" s="9">
+      <c r="J15" s="12">
         <v>2750.0</v>
       </c>
-      <c r="K15" s="10">
+      <c r="K15" s="13">
         <v>204000.0</v>
       </c>
-      <c r="L15" s="11">
+      <c r="L15" s="14">
         <f>Assumptions!$B$6</f>
         <v>0.00016558</v>
       </c>
@@ -6308,59 +6796,59 @@
         <f t="shared" si="2"/>
         <v>3752.07</v>
       </c>
-      <c r="Q15" s="9" t="s">
+      <c r="Q15" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="R15" s="8">
-        <v>2.6</v>
-      </c>
-      <c r="S15" s="10">
-        <v>2.0E-10</v>
-      </c>
-      <c r="T15" s="17"/>
-      <c r="U15" s="17"/>
-      <c r="V15" s="17"/>
-      <c r="W15" s="13" t="str">
+      <c r="R15" s="15">
+        <v>2.58</v>
+      </c>
+      <c r="S15" s="16">
+        <v>6.0E-11</v>
+      </c>
+      <c r="T15" s="27"/>
+      <c r="U15" s="27"/>
+      <c r="V15" s="27"/>
+      <c r="W15" s="26" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="X15" s="13" t="str">
+      <c r="X15" s="26" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="Y15" s="17"/>
+      <c r="Y15" s="27"/>
       <c r="Z15" s="6" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="AA15" s="18"/>
-      <c r="AB15" s="17"/>
-      <c r="AC15" s="18"/>
-      <c r="AD15" s="17"/>
+      <c r="AA15" s="28"/>
+      <c r="AB15" s="27"/>
+      <c r="AC15" s="28"/>
+      <c r="AD15" s="27"/>
       <c r="AE15" s="6" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="AF15" s="18"/>
-      <c r="AG15" s="17"/>
-      <c r="AH15" s="18"/>
-      <c r="AI15" s="17"/>
+      <c r="AF15" s="28"/>
+      <c r="AG15" s="27"/>
+      <c r="AH15" s="28"/>
+      <c r="AI15" s="27"/>
       <c r="AJ15" s="6" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="AK15" s="18"/>
-      <c r="AL15" s="19"/>
-      <c r="AM15" s="18"/>
-      <c r="AN15" s="19"/>
+      <c r="AK15" s="28"/>
+      <c r="AL15" s="29"/>
+      <c r="AM15" s="28"/>
+      <c r="AN15" s="29"/>
       <c r="AO15" s="6" t="str">
         <f>IF(OR(AK15="",AL15="",AM15="",AN15=""),"",AK15+(Assumptions!$B$8-AL15)/(AN15-AL15)*(AM15-AK15))</f>
         <v/>
       </c>
-      <c r="AP15" s="18"/>
-      <c r="AQ15" s="19"/>
-      <c r="AR15" s="18"/>
-      <c r="AS15" s="19"/>
+      <c r="AP15" s="28"/>
+      <c r="AQ15" s="29"/>
+      <c r="AR15" s="28"/>
+      <c r="AS15" s="29"/>
       <c r="AT15" s="6" t="str">
         <f>IF(OR(AP15="",AQ15="",AR15="",AS15=""),"",AP15+(Assumptions!$B$9-AQ15)/(AS15-AQ15)*(AR15-AP15))</f>
         <v/>
@@ -6369,7 +6857,18 @@
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="AV15" s="16"/>
+      <c r="AV15" s="23">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AW15" s="23">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="AX15" s="24">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="5">
@@ -6387,25 +6886,25 @@
       <c r="E16" s="5">
         <v>3.0</v>
       </c>
-      <c r="F16" s="8">
+      <c r="F16" s="11">
         <v>298.15</v>
       </c>
-      <c r="G16" s="8">
+      <c r="G16" s="11">
         <v>8.0</v>
       </c>
-      <c r="H16" s="9" t="s">
+      <c r="H16" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="I16" s="9">
+      <c r="I16" s="12">
         <v>500.0</v>
       </c>
-      <c r="J16" s="9">
+      <c r="J16" s="12">
         <v>2750.0</v>
       </c>
-      <c r="K16" s="10">
+      <c r="K16" s="13">
         <v>186000.0</v>
       </c>
-      <c r="L16" s="11">
+      <c r="L16" s="14">
         <f>Assumptions!$B$6</f>
         <v>0.00016558</v>
       </c>
@@ -6425,59 +6924,59 @@
         <f t="shared" si="2"/>
         <v>3206.725</v>
       </c>
-      <c r="Q16" s="9" t="s">
+      <c r="Q16" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="R16" s="8">
-        <v>2.8</v>
-      </c>
-      <c r="S16" s="10">
-        <v>5.0E-11</v>
-      </c>
-      <c r="T16" s="17"/>
-      <c r="U16" s="17"/>
-      <c r="V16" s="17"/>
-      <c r="W16" s="13" t="str">
+      <c r="R16" s="15">
+        <v>2.77</v>
+      </c>
+      <c r="S16" s="16">
+        <v>6.0E-11</v>
+      </c>
+      <c r="T16" s="27"/>
+      <c r="U16" s="27"/>
+      <c r="V16" s="27"/>
+      <c r="W16" s="26" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="X16" s="13" t="str">
+      <c r="X16" s="26" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="Y16" s="17"/>
+      <c r="Y16" s="27"/>
       <c r="Z16" s="6" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="AA16" s="18"/>
-      <c r="AB16" s="17"/>
-      <c r="AC16" s="18"/>
-      <c r="AD16" s="17"/>
+      <c r="AA16" s="28"/>
+      <c r="AB16" s="27"/>
+      <c r="AC16" s="28"/>
+      <c r="AD16" s="27"/>
       <c r="AE16" s="6" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="AF16" s="18"/>
-      <c r="AG16" s="17"/>
-      <c r="AH16" s="18"/>
-      <c r="AI16" s="17"/>
+      <c r="AF16" s="28"/>
+      <c r="AG16" s="27"/>
+      <c r="AH16" s="28"/>
+      <c r="AI16" s="27"/>
       <c r="AJ16" s="6" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="AK16" s="18"/>
-      <c r="AL16" s="19"/>
-      <c r="AM16" s="18"/>
-      <c r="AN16" s="19"/>
+      <c r="AK16" s="28"/>
+      <c r="AL16" s="29"/>
+      <c r="AM16" s="28"/>
+      <c r="AN16" s="29"/>
       <c r="AO16" s="6" t="str">
         <f>IF(OR(AK16="",AL16="",AM16="",AN16=""),"",AK16+(Assumptions!$B$8-AL16)/(AN16-AL16)*(AM16-AK16))</f>
         <v/>
       </c>
-      <c r="AP16" s="18"/>
-      <c r="AQ16" s="19"/>
-      <c r="AR16" s="18"/>
-      <c r="AS16" s="19"/>
+      <c r="AP16" s="28"/>
+      <c r="AQ16" s="29"/>
+      <c r="AR16" s="28"/>
+      <c r="AS16" s="29"/>
       <c r="AT16" s="6" t="str">
         <f>IF(OR(AP16="",AQ16="",AR16="",AS16=""),"",AP16+(Assumptions!$B$9-AQ16)/(AS16-AQ16)*(AR16-AP16))</f>
         <v/>
@@ -6486,7 +6985,18 @@
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="AV16" s="16"/>
+      <c r="AV16" s="23">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AW16" s="23">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="AX16" s="24">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="5">
@@ -6504,25 +7014,25 @@
       <c r="E17" s="5">
         <v>1.0</v>
       </c>
-      <c r="F17" s="8">
+      <c r="F17" s="11">
         <v>298.15</v>
       </c>
-      <c r="G17" s="8">
+      <c r="G17" s="11">
         <v>8.0</v>
       </c>
-      <c r="H17" s="9" t="s">
+      <c r="H17" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="I17" s="9">
+      <c r="I17" s="12">
         <v>550.0</v>
       </c>
-      <c r="J17" s="9">
+      <c r="J17" s="12">
         <v>2750.0</v>
       </c>
-      <c r="K17" s="10">
+      <c r="K17" s="13">
         <v>200000.0</v>
       </c>
-      <c r="L17" s="11">
+      <c r="L17" s="14">
         <f>Assumptions!$B$6</f>
         <v>0.00016558</v>
       </c>
@@ -6542,59 +7052,59 @@
         <f t="shared" si="2"/>
         <v>3504.3975</v>
       </c>
-      <c r="Q17" s="9" t="s">
+      <c r="Q17" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="R17" s="8">
-        <v>2.6</v>
-      </c>
-      <c r="S17" s="10">
-        <v>2.0E-10</v>
-      </c>
-      <c r="T17" s="17"/>
-      <c r="U17" s="17"/>
-      <c r="V17" s="17"/>
-      <c r="W17" s="13" t="str">
+      <c r="R17" s="15">
+        <v>2.58</v>
+      </c>
+      <c r="S17" s="16">
+        <v>2.0E-11</v>
+      </c>
+      <c r="T17" s="27"/>
+      <c r="U17" s="27"/>
+      <c r="V17" s="27"/>
+      <c r="W17" s="26" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="X17" s="13" t="str">
+      <c r="X17" s="26" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="Y17" s="17"/>
+      <c r="Y17" s="27"/>
       <c r="Z17" s="6" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="AA17" s="18"/>
-      <c r="AB17" s="17"/>
-      <c r="AC17" s="18"/>
-      <c r="AD17" s="17"/>
+      <c r="AA17" s="28"/>
+      <c r="AB17" s="27"/>
+      <c r="AC17" s="28"/>
+      <c r="AD17" s="27"/>
       <c r="AE17" s="6" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="AF17" s="18"/>
-      <c r="AG17" s="17"/>
-      <c r="AH17" s="18"/>
-      <c r="AI17" s="17"/>
+      <c r="AF17" s="28"/>
+      <c r="AG17" s="27"/>
+      <c r="AH17" s="28"/>
+      <c r="AI17" s="27"/>
       <c r="AJ17" s="6" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="AK17" s="18"/>
-      <c r="AL17" s="19"/>
-      <c r="AM17" s="18"/>
-      <c r="AN17" s="19"/>
+      <c r="AK17" s="28"/>
+      <c r="AL17" s="29"/>
+      <c r="AM17" s="28"/>
+      <c r="AN17" s="29"/>
       <c r="AO17" s="6" t="str">
         <f>IF(OR(AK17="",AL17="",AM17="",AN17=""),"",AK17+(Assumptions!$B$8-AL17)/(AN17-AL17)*(AM17-AK17))</f>
         <v/>
       </c>
-      <c r="AP17" s="18"/>
-      <c r="AQ17" s="19"/>
-      <c r="AR17" s="18"/>
-      <c r="AS17" s="19"/>
+      <c r="AP17" s="28"/>
+      <c r="AQ17" s="29"/>
+      <c r="AR17" s="28"/>
+      <c r="AS17" s="29"/>
       <c r="AT17" s="6" t="str">
         <f>IF(OR(AP17="",AQ17="",AR17="",AS17=""),"",AP17+(Assumptions!$B$9-AQ17)/(AS17-AQ17)*(AR17-AP17))</f>
         <v/>
@@ -6603,7 +7113,18 @@
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="AV17" s="16"/>
+      <c r="AV17" s="23">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AW17" s="23">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="AX17" s="24">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="5">
@@ -6621,25 +7142,25 @@
       <c r="E18" s="5">
         <v>2.0</v>
       </c>
-      <c r="F18" s="8">
+      <c r="F18" s="11">
         <v>298.15</v>
       </c>
-      <c r="G18" s="8">
+      <c r="G18" s="11">
         <v>8.0</v>
       </c>
-      <c r="H18" s="9" t="s">
+      <c r="H18" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="I18" s="9">
+      <c r="I18" s="12">
         <v>600.0</v>
       </c>
-      <c r="J18" s="9">
+      <c r="J18" s="12">
         <v>2750.0</v>
       </c>
-      <c r="K18" s="10">
+      <c r="K18" s="13">
         <v>204000.0</v>
       </c>
-      <c r="L18" s="11">
+      <c r="L18" s="14">
         <f>Assumptions!$B$6</f>
         <v>0.00016558</v>
       </c>
@@ -6659,59 +7180,59 @@
         <f t="shared" si="2"/>
         <v>3752.07</v>
       </c>
-      <c r="Q18" s="9" t="s">
+      <c r="Q18" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="R18" s="8">
-        <v>2.7</v>
-      </c>
-      <c r="S18" s="10">
-        <v>1.0E-10</v>
-      </c>
-      <c r="T18" s="17"/>
-      <c r="U18" s="17"/>
-      <c r="V18" s="17"/>
-      <c r="W18" s="13" t="str">
+      <c r="R18" s="15">
+        <v>2.68</v>
+      </c>
+      <c r="S18" s="16">
+        <v>5.0E-12</v>
+      </c>
+      <c r="T18" s="27"/>
+      <c r="U18" s="27"/>
+      <c r="V18" s="27"/>
+      <c r="W18" s="26" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="X18" s="13" t="str">
+      <c r="X18" s="26" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="Y18" s="17"/>
+      <c r="Y18" s="27"/>
       <c r="Z18" s="6" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="AA18" s="18"/>
-      <c r="AB18" s="17"/>
-      <c r="AC18" s="18"/>
-      <c r="AD18" s="17"/>
+      <c r="AA18" s="28"/>
+      <c r="AB18" s="27"/>
+      <c r="AC18" s="28"/>
+      <c r="AD18" s="27"/>
       <c r="AE18" s="6" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="AF18" s="18"/>
-      <c r="AG18" s="17"/>
-      <c r="AH18" s="18"/>
-      <c r="AI18" s="17"/>
+      <c r="AF18" s="28"/>
+      <c r="AG18" s="27"/>
+      <c r="AH18" s="28"/>
+      <c r="AI18" s="27"/>
       <c r="AJ18" s="6" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="AK18" s="18"/>
-      <c r="AL18" s="19"/>
-      <c r="AM18" s="18"/>
-      <c r="AN18" s="19"/>
+      <c r="AK18" s="28"/>
+      <c r="AL18" s="29"/>
+      <c r="AM18" s="28"/>
+      <c r="AN18" s="29"/>
       <c r="AO18" s="6" t="str">
         <f>IF(OR(AK18="",AL18="",AM18="",AN18=""),"",AK18+(Assumptions!$B$8-AL18)/(AN18-AL18)*(AM18-AK18))</f>
         <v/>
       </c>
-      <c r="AP18" s="18"/>
-      <c r="AQ18" s="19"/>
-      <c r="AR18" s="18"/>
-      <c r="AS18" s="19"/>
+      <c r="AP18" s="28"/>
+      <c r="AQ18" s="29"/>
+      <c r="AR18" s="28"/>
+      <c r="AS18" s="29"/>
       <c r="AT18" s="6" t="str">
         <f>IF(OR(AP18="",AQ18="",AR18="",AS18=""),"",AP18+(Assumptions!$B$9-AQ18)/(AS18-AQ18)*(AR18-AP18))</f>
         <v/>
@@ -6720,7 +7241,18 @@
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="AV18" s="16"/>
+      <c r="AV18" s="23">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AW18" s="23">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="AX18" s="24">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="5">
@@ -6738,25 +7270,25 @@
       <c r="E19" s="5">
         <v>1.0</v>
       </c>
-      <c r="F19" s="8">
+      <c r="F19" s="11">
         <v>298.15</v>
       </c>
-      <c r="G19" s="8">
+      <c r="G19" s="11">
         <v>12.0</v>
       </c>
-      <c r="H19" s="9" t="s">
+      <c r="H19" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="I19" s="9">
+      <c r="I19" s="12">
         <v>500.0</v>
       </c>
-      <c r="J19" s="9">
+      <c r="J19" s="12">
         <v>2750.0</v>
       </c>
-      <c r="K19" s="10">
+      <c r="K19" s="13">
         <v>186000.0</v>
       </c>
-      <c r="L19" s="11">
+      <c r="L19" s="14">
         <f>Assumptions!$B$6</f>
         <v>0.00016558</v>
       </c>
@@ -6776,59 +7308,59 @@
         <f t="shared" si="2"/>
         <v>3206.725</v>
       </c>
-      <c r="Q19" s="9" t="s">
+      <c r="Q19" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="R19" s="8">
-        <v>2.6</v>
-      </c>
-      <c r="S19" s="10">
-        <v>2.0E-10</v>
-      </c>
-      <c r="T19" s="17"/>
-      <c r="U19" s="17"/>
-      <c r="V19" s="17"/>
-      <c r="W19" s="13" t="str">
+      <c r="R19" s="15">
+        <v>2.58</v>
+      </c>
+      <c r="S19" s="16">
+        <v>5.0E-12</v>
+      </c>
+      <c r="T19" s="27"/>
+      <c r="U19" s="27"/>
+      <c r="V19" s="27"/>
+      <c r="W19" s="26" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="X19" s="13" t="str">
+      <c r="X19" s="26" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="Y19" s="17"/>
+      <c r="Y19" s="27"/>
       <c r="Z19" s="6" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="AA19" s="18"/>
-      <c r="AB19" s="17"/>
-      <c r="AC19" s="18"/>
-      <c r="AD19" s="17"/>
+      <c r="AA19" s="28"/>
+      <c r="AB19" s="27"/>
+      <c r="AC19" s="28"/>
+      <c r="AD19" s="27"/>
       <c r="AE19" s="6" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="AF19" s="18"/>
-      <c r="AG19" s="17"/>
-      <c r="AH19" s="18"/>
-      <c r="AI19" s="17"/>
+      <c r="AF19" s="28"/>
+      <c r="AG19" s="27"/>
+      <c r="AH19" s="28"/>
+      <c r="AI19" s="27"/>
       <c r="AJ19" s="6" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="AK19" s="18"/>
-      <c r="AL19" s="19"/>
-      <c r="AM19" s="18"/>
-      <c r="AN19" s="19"/>
+      <c r="AK19" s="28"/>
+      <c r="AL19" s="29"/>
+      <c r="AM19" s="28"/>
+      <c r="AN19" s="29"/>
       <c r="AO19" s="6" t="str">
         <f>IF(OR(AK19="",AL19="",AM19="",AN19=""),"",AK19+(Assumptions!$B$8-AL19)/(AN19-AL19)*(AM19-AK19))</f>
         <v/>
       </c>
-      <c r="AP19" s="18"/>
-      <c r="AQ19" s="19"/>
-      <c r="AR19" s="18"/>
-      <c r="AS19" s="19"/>
+      <c r="AP19" s="28"/>
+      <c r="AQ19" s="29"/>
+      <c r="AR19" s="28"/>
+      <c r="AS19" s="29"/>
       <c r="AT19" s="6" t="str">
         <f>IF(OR(AP19="",AQ19="",AR19="",AS19=""),"",AP19+(Assumptions!$B$9-AQ19)/(AS19-AQ19)*(AR19-AP19))</f>
         <v/>
@@ -6837,7 +7369,18 @@
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="AV19" s="16"/>
+      <c r="AV19" s="23">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AW19" s="23">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="AX19" s="24">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="5">
@@ -6855,25 +7398,25 @@
       <c r="E20" s="5">
         <v>2.0</v>
       </c>
-      <c r="F20" s="8">
+      <c r="F20" s="11">
         <v>298.15</v>
       </c>
-      <c r="G20" s="8">
+      <c r="G20" s="11">
         <v>12.0</v>
       </c>
-      <c r="H20" s="9" t="s">
+      <c r="H20" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="I20" s="9">
+      <c r="I20" s="12">
         <v>550.0</v>
       </c>
-      <c r="J20" s="9">
+      <c r="J20" s="12">
         <v>2750.0</v>
       </c>
-      <c r="K20" s="10">
+      <c r="K20" s="13">
         <v>200000.0</v>
       </c>
-      <c r="L20" s="11">
+      <c r="L20" s="14">
         <f>Assumptions!$B$6</f>
         <v>0.00016558</v>
       </c>
@@ -6893,59 +7436,59 @@
         <f t="shared" si="2"/>
         <v>3504.3975</v>
       </c>
-      <c r="Q20" s="9" t="s">
+      <c r="Q20" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="R20" s="8">
-        <v>2.7</v>
-      </c>
-      <c r="S20" s="10">
-        <v>1.0E-10</v>
-      </c>
-      <c r="T20" s="17"/>
-      <c r="U20" s="17"/>
-      <c r="V20" s="17"/>
-      <c r="W20" s="13" t="str">
+      <c r="R20" s="15">
+        <v>2.68</v>
+      </c>
+      <c r="S20" s="16">
+        <v>6.0E-11</v>
+      </c>
+      <c r="T20" s="27"/>
+      <c r="U20" s="27"/>
+      <c r="V20" s="27"/>
+      <c r="W20" s="26" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="X20" s="13" t="str">
+      <c r="X20" s="26" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="Y20" s="17"/>
+      <c r="Y20" s="27"/>
       <c r="Z20" s="6" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="AA20" s="18"/>
-      <c r="AB20" s="17"/>
-      <c r="AC20" s="18"/>
-      <c r="AD20" s="17"/>
+      <c r="AA20" s="28"/>
+      <c r="AB20" s="27"/>
+      <c r="AC20" s="28"/>
+      <c r="AD20" s="27"/>
       <c r="AE20" s="6" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="AF20" s="18"/>
-      <c r="AG20" s="17"/>
-      <c r="AH20" s="18"/>
-      <c r="AI20" s="17"/>
+      <c r="AF20" s="28"/>
+      <c r="AG20" s="27"/>
+      <c r="AH20" s="28"/>
+      <c r="AI20" s="27"/>
       <c r="AJ20" s="6" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="AK20" s="18"/>
-      <c r="AL20" s="19"/>
-      <c r="AM20" s="18"/>
-      <c r="AN20" s="19"/>
+      <c r="AK20" s="28"/>
+      <c r="AL20" s="29"/>
+      <c r="AM20" s="28"/>
+      <c r="AN20" s="29"/>
       <c r="AO20" s="6" t="str">
         <f>IF(OR(AK20="",AL20="",AM20="",AN20=""),"",AK20+(Assumptions!$B$8-AL20)/(AN20-AL20)*(AM20-AK20))</f>
         <v/>
       </c>
-      <c r="AP20" s="18"/>
-      <c r="AQ20" s="19"/>
-      <c r="AR20" s="18"/>
-      <c r="AS20" s="19"/>
+      <c r="AP20" s="28"/>
+      <c r="AQ20" s="29"/>
+      <c r="AR20" s="28"/>
+      <c r="AS20" s="29"/>
       <c r="AT20" s="6" t="str">
         <f>IF(OR(AP20="",AQ20="",AR20="",AS20=""),"",AP20+(Assumptions!$B$9-AQ20)/(AS20-AQ20)*(AR20-AP20))</f>
         <v/>
@@ -6954,7 +7497,18 @@
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="AV20" s="16"/>
+      <c r="AV20" s="23">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AW20" s="23">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="AX20" s="24">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="5">
@@ -6972,25 +7526,25 @@
       <c r="E21" s="5">
         <v>3.0</v>
       </c>
-      <c r="F21" s="8">
+      <c r="F21" s="11">
         <v>298.15</v>
       </c>
-      <c r="G21" s="8">
+      <c r="G21" s="11">
         <v>12.0</v>
       </c>
-      <c r="H21" s="9" t="s">
+      <c r="H21" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="I21" s="9">
+      <c r="I21" s="12">
         <v>600.0</v>
       </c>
-      <c r="J21" s="9">
+      <c r="J21" s="12">
         <v>2750.0</v>
       </c>
-      <c r="K21" s="10">
+      <c r="K21" s="13">
         <v>204000.0</v>
       </c>
-      <c r="L21" s="11">
+      <c r="L21" s="14">
         <f>Assumptions!$B$6</f>
         <v>0.00016558</v>
       </c>
@@ -7010,59 +7564,59 @@
         <f t="shared" si="2"/>
         <v>3752.07</v>
       </c>
-      <c r="Q21" s="9" t="s">
+      <c r="Q21" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="R21" s="8">
-        <v>2.8</v>
-      </c>
-      <c r="S21" s="10">
-        <v>5.0E-11</v>
-      </c>
-      <c r="T21" s="17"/>
-      <c r="U21" s="17"/>
-      <c r="V21" s="17"/>
-      <c r="W21" s="13" t="str">
+      <c r="R21" s="15">
+        <v>2.77</v>
+      </c>
+      <c r="S21" s="16">
+        <v>2.0E-11</v>
+      </c>
+      <c r="T21" s="27"/>
+      <c r="U21" s="27"/>
+      <c r="V21" s="27"/>
+      <c r="W21" s="26" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="X21" s="13" t="str">
+      <c r="X21" s="26" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="Y21" s="17"/>
+      <c r="Y21" s="27"/>
       <c r="Z21" s="6" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="AA21" s="18"/>
-      <c r="AB21" s="17"/>
-      <c r="AC21" s="18"/>
-      <c r="AD21" s="17"/>
+      <c r="AA21" s="28"/>
+      <c r="AB21" s="27"/>
+      <c r="AC21" s="28"/>
+      <c r="AD21" s="27"/>
       <c r="AE21" s="6" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="AF21" s="18"/>
-      <c r="AG21" s="17"/>
-      <c r="AH21" s="18"/>
-      <c r="AI21" s="17"/>
+      <c r="AF21" s="28"/>
+      <c r="AG21" s="27"/>
+      <c r="AH21" s="28"/>
+      <c r="AI21" s="27"/>
       <c r="AJ21" s="6" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="AK21" s="18"/>
-      <c r="AL21" s="19"/>
-      <c r="AM21" s="18"/>
-      <c r="AN21" s="19"/>
+      <c r="AK21" s="28"/>
+      <c r="AL21" s="29"/>
+      <c r="AM21" s="28"/>
+      <c r="AN21" s="29"/>
       <c r="AO21" s="6" t="str">
         <f>IF(OR(AK21="",AL21="",AM21="",AN21=""),"",AK21+(Assumptions!$B$8-AL21)/(AN21-AL21)*(AM21-AK21))</f>
         <v/>
       </c>
-      <c r="AP21" s="18"/>
-      <c r="AQ21" s="19"/>
-      <c r="AR21" s="18"/>
-      <c r="AS21" s="19"/>
+      <c r="AP21" s="28"/>
+      <c r="AQ21" s="29"/>
+      <c r="AR21" s="28"/>
+      <c r="AS21" s="29"/>
       <c r="AT21" s="6" t="str">
         <f>IF(OR(AP21="",AQ21="",AR21="",AS21=""),"",AP21+(Assumptions!$B$9-AQ21)/(AS21-AQ21)*(AR21-AP21))</f>
         <v/>
@@ -7071,7 +7625,18 @@
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="AV21" s="16"/>
+      <c r="AV21" s="23">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AW21" s="23">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="AX21" s="24">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="5">
@@ -7089,25 +7654,25 @@
       <c r="E22" s="5">
         <v>3.0</v>
       </c>
-      <c r="F22" s="8">
+      <c r="F22" s="11">
         <v>303.15</v>
       </c>
-      <c r="G22" s="8">
+      <c r="G22" s="11">
         <v>5.0</v>
       </c>
-      <c r="H22" s="9" t="s">
+      <c r="H22" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="I22" s="9">
+      <c r="I22" s="12">
         <v>500.0</v>
       </c>
-      <c r="J22" s="9">
+      <c r="J22" s="12">
         <v>2750.0</v>
       </c>
-      <c r="K22" s="10">
+      <c r="K22" s="13">
         <v>186000.0</v>
       </c>
-      <c r="L22" s="11">
+      <c r="L22" s="14">
         <f>Assumptions!$B$6</f>
         <v>0.00016558</v>
       </c>
@@ -7127,59 +7692,59 @@
         <f t="shared" si="2"/>
         <v>3206.725</v>
       </c>
-      <c r="Q22" s="9" t="s">
+      <c r="Q22" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="R22" s="8">
-        <v>2.8</v>
-      </c>
-      <c r="S22" s="10">
-        <v>5.0E-11</v>
-      </c>
-      <c r="T22" s="17"/>
-      <c r="U22" s="17"/>
-      <c r="V22" s="17"/>
-      <c r="W22" s="13" t="str">
+      <c r="R22" s="15">
+        <v>2.77</v>
+      </c>
+      <c r="S22" s="16">
+        <v>6.0E-11</v>
+      </c>
+      <c r="T22" s="27"/>
+      <c r="U22" s="27"/>
+      <c r="V22" s="27"/>
+      <c r="W22" s="26" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="X22" s="13" t="str">
+      <c r="X22" s="26" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="Y22" s="17"/>
+      <c r="Y22" s="27"/>
       <c r="Z22" s="6" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="AA22" s="18"/>
-      <c r="AB22" s="17"/>
-      <c r="AC22" s="18"/>
-      <c r="AD22" s="17"/>
+      <c r="AA22" s="28"/>
+      <c r="AB22" s="27"/>
+      <c r="AC22" s="28"/>
+      <c r="AD22" s="27"/>
       <c r="AE22" s="6" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="AF22" s="18"/>
-      <c r="AG22" s="17"/>
-      <c r="AH22" s="18"/>
-      <c r="AI22" s="17"/>
+      <c r="AF22" s="28"/>
+      <c r="AG22" s="27"/>
+      <c r="AH22" s="28"/>
+      <c r="AI22" s="27"/>
       <c r="AJ22" s="6" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="AK22" s="18"/>
-      <c r="AL22" s="19"/>
-      <c r="AM22" s="18"/>
-      <c r="AN22" s="19"/>
+      <c r="AK22" s="28"/>
+      <c r="AL22" s="29"/>
+      <c r="AM22" s="28"/>
+      <c r="AN22" s="29"/>
       <c r="AO22" s="6" t="str">
         <f>IF(OR(AK22="",AL22="",AM22="",AN22=""),"",AK22+(Assumptions!$B$8-AL22)/(AN22-AL22)*(AM22-AK22))</f>
         <v/>
       </c>
-      <c r="AP22" s="18"/>
-      <c r="AQ22" s="19"/>
-      <c r="AR22" s="18"/>
-      <c r="AS22" s="19"/>
+      <c r="AP22" s="28"/>
+      <c r="AQ22" s="29"/>
+      <c r="AR22" s="28"/>
+      <c r="AS22" s="29"/>
       <c r="AT22" s="6" t="str">
         <f>IF(OR(AP22="",AQ22="",AR22="",AS22=""),"",AP22+(Assumptions!$B$9-AQ22)/(AS22-AQ22)*(AR22-AP22))</f>
         <v/>
@@ -7188,7 +7753,18 @@
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="AV22" s="16"/>
+      <c r="AV22" s="23">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AW22" s="23">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="AX22" s="24">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="5">
@@ -7206,25 +7782,25 @@
       <c r="E23" s="5">
         <v>1.0</v>
       </c>
-      <c r="F23" s="8">
+      <c r="F23" s="11">
         <v>303.15</v>
       </c>
-      <c r="G23" s="8">
+      <c r="G23" s="11">
         <v>5.0</v>
       </c>
-      <c r="H23" s="9" t="s">
+      <c r="H23" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="I23" s="9">
+      <c r="I23" s="12">
         <v>550.0</v>
       </c>
-      <c r="J23" s="9">
+      <c r="J23" s="12">
         <v>2750.0</v>
       </c>
-      <c r="K23" s="10">
+      <c r="K23" s="13">
         <v>200000.0</v>
       </c>
-      <c r="L23" s="11">
+      <c r="L23" s="14">
         <f>Assumptions!$B$6</f>
         <v>0.00016558</v>
       </c>
@@ -7244,59 +7820,59 @@
         <f t="shared" si="2"/>
         <v>3504.3975</v>
       </c>
-      <c r="Q23" s="9" t="s">
+      <c r="Q23" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="R23" s="8">
-        <v>2.6</v>
-      </c>
-      <c r="S23" s="10">
-        <v>2.0E-10</v>
-      </c>
-      <c r="T23" s="17"/>
-      <c r="U23" s="17"/>
-      <c r="V23" s="17"/>
-      <c r="W23" s="13" t="str">
+      <c r="R23" s="15">
+        <v>2.58</v>
+      </c>
+      <c r="S23" s="16">
+        <v>2.0E-11</v>
+      </c>
+      <c r="T23" s="27"/>
+      <c r="U23" s="27"/>
+      <c r="V23" s="27"/>
+      <c r="W23" s="26" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="X23" s="13" t="str">
+      <c r="X23" s="26" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="Y23" s="17"/>
+      <c r="Y23" s="27"/>
       <c r="Z23" s="6" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="AA23" s="18"/>
-      <c r="AB23" s="17"/>
-      <c r="AC23" s="18"/>
-      <c r="AD23" s="17"/>
+      <c r="AA23" s="28"/>
+      <c r="AB23" s="27"/>
+      <c r="AC23" s="28"/>
+      <c r="AD23" s="27"/>
       <c r="AE23" s="6" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="AF23" s="18"/>
-      <c r="AG23" s="17"/>
-      <c r="AH23" s="18"/>
-      <c r="AI23" s="17"/>
+      <c r="AF23" s="28"/>
+      <c r="AG23" s="27"/>
+      <c r="AH23" s="28"/>
+      <c r="AI23" s="27"/>
       <c r="AJ23" s="6" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="AK23" s="18"/>
-      <c r="AL23" s="19"/>
-      <c r="AM23" s="18"/>
-      <c r="AN23" s="19"/>
+      <c r="AK23" s="28"/>
+      <c r="AL23" s="29"/>
+      <c r="AM23" s="28"/>
+      <c r="AN23" s="29"/>
       <c r="AO23" s="6" t="str">
         <f>IF(OR(AK23="",AL23="",AM23="",AN23=""),"",AK23+(Assumptions!$B$8-AL23)/(AN23-AL23)*(AM23-AK23))</f>
         <v/>
       </c>
-      <c r="AP23" s="18"/>
-      <c r="AQ23" s="19"/>
-      <c r="AR23" s="18"/>
-      <c r="AS23" s="19"/>
+      <c r="AP23" s="28"/>
+      <c r="AQ23" s="29"/>
+      <c r="AR23" s="28"/>
+      <c r="AS23" s="29"/>
       <c r="AT23" s="6" t="str">
         <f>IF(OR(AP23="",AQ23="",AR23="",AS23=""),"",AP23+(Assumptions!$B$9-AQ23)/(AS23-AQ23)*(AR23-AP23))</f>
         <v/>
@@ -7305,7 +7881,18 @@
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="AV23" s="16"/>
+      <c r="AV23" s="23">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AW23" s="23">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="AX23" s="24">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
       <c r="A24" s="5">
@@ -7323,25 +7910,25 @@
       <c r="E24" s="5">
         <v>2.0</v>
       </c>
-      <c r="F24" s="8">
+      <c r="F24" s="11">
         <v>303.15</v>
       </c>
-      <c r="G24" s="8">
+      <c r="G24" s="11">
         <v>5.0</v>
       </c>
-      <c r="H24" s="9" t="s">
+      <c r="H24" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="I24" s="9">
+      <c r="I24" s="12">
         <v>600.0</v>
       </c>
-      <c r="J24" s="9">
+      <c r="J24" s="12">
         <v>2750.0</v>
       </c>
-      <c r="K24" s="10">
+      <c r="K24" s="13">
         <v>204000.0</v>
       </c>
-      <c r="L24" s="11">
+      <c r="L24" s="14">
         <f>Assumptions!$B$6</f>
         <v>0.00016558</v>
       </c>
@@ -7361,59 +7948,59 @@
         <f t="shared" si="2"/>
         <v>3752.07</v>
       </c>
-      <c r="Q24" s="9" t="s">
+      <c r="Q24" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="R24" s="8">
-        <v>2.7</v>
-      </c>
-      <c r="S24" s="10">
-        <v>1.0E-10</v>
-      </c>
-      <c r="T24" s="17"/>
-      <c r="U24" s="17"/>
-      <c r="V24" s="17"/>
-      <c r="W24" s="13" t="str">
+      <c r="R24" s="15">
+        <v>2.68</v>
+      </c>
+      <c r="S24" s="16">
+        <v>5.0E-12</v>
+      </c>
+      <c r="T24" s="27"/>
+      <c r="U24" s="27"/>
+      <c r="V24" s="27"/>
+      <c r="W24" s="26" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="X24" s="13" t="str">
+      <c r="X24" s="26" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="Y24" s="17"/>
+      <c r="Y24" s="27"/>
       <c r="Z24" s="6" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="AA24" s="18"/>
-      <c r="AB24" s="17"/>
-      <c r="AC24" s="18"/>
-      <c r="AD24" s="17"/>
+      <c r="AA24" s="28"/>
+      <c r="AB24" s="27"/>
+      <c r="AC24" s="28"/>
+      <c r="AD24" s="27"/>
       <c r="AE24" s="6" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="AF24" s="18"/>
-      <c r="AG24" s="17"/>
-      <c r="AH24" s="18"/>
-      <c r="AI24" s="17"/>
+      <c r="AF24" s="28"/>
+      <c r="AG24" s="27"/>
+      <c r="AH24" s="28"/>
+      <c r="AI24" s="27"/>
       <c r="AJ24" s="6" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="AK24" s="18"/>
-      <c r="AL24" s="19"/>
-      <c r="AM24" s="18"/>
-      <c r="AN24" s="19"/>
+      <c r="AK24" s="28"/>
+      <c r="AL24" s="29"/>
+      <c r="AM24" s="28"/>
+      <c r="AN24" s="29"/>
       <c r="AO24" s="6" t="str">
         <f>IF(OR(AK24="",AL24="",AM24="",AN24=""),"",AK24+(Assumptions!$B$8-AL24)/(AN24-AL24)*(AM24-AK24))</f>
         <v/>
       </c>
-      <c r="AP24" s="18"/>
-      <c r="AQ24" s="19"/>
-      <c r="AR24" s="18"/>
-      <c r="AS24" s="19"/>
+      <c r="AP24" s="28"/>
+      <c r="AQ24" s="29"/>
+      <c r="AR24" s="28"/>
+      <c r="AS24" s="29"/>
       <c r="AT24" s="6" t="str">
         <f>IF(OR(AP24="",AQ24="",AR24="",AS24=""),"",AP24+(Assumptions!$B$9-AQ24)/(AS24-AQ24)*(AR24-AP24))</f>
         <v/>
@@ -7422,7 +8009,18 @@
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="AV24" s="16"/>
+      <c r="AV24" s="23">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AW24" s="23">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="AX24" s="24">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="25" ht="15.75" customHeight="1">
       <c r="A25" s="5">
@@ -7440,25 +8038,25 @@
       <c r="E25" s="5">
         <v>1.0</v>
       </c>
-      <c r="F25" s="8">
+      <c r="F25" s="11">
         <v>303.15</v>
       </c>
-      <c r="G25" s="8">
+      <c r="G25" s="11">
         <v>8.0</v>
       </c>
-      <c r="H25" s="9" t="s">
+      <c r="H25" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="I25" s="9">
+      <c r="I25" s="12">
         <v>500.0</v>
       </c>
-      <c r="J25" s="9">
+      <c r="J25" s="12">
         <v>2750.0</v>
       </c>
-      <c r="K25" s="10">
+      <c r="K25" s="13">
         <v>186000.0</v>
       </c>
-      <c r="L25" s="11">
+      <c r="L25" s="14">
         <f>Assumptions!$B$6</f>
         <v>0.00016558</v>
       </c>
@@ -7478,59 +8076,59 @@
         <f t="shared" si="2"/>
         <v>3206.725</v>
       </c>
-      <c r="Q25" s="9" t="s">
+      <c r="Q25" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="R25" s="8">
-        <v>2.6</v>
-      </c>
-      <c r="S25" s="10">
-        <v>2.0E-10</v>
-      </c>
-      <c r="T25" s="17"/>
-      <c r="U25" s="17"/>
-      <c r="V25" s="17"/>
-      <c r="W25" s="13" t="str">
+      <c r="R25" s="15">
+        <v>2.58</v>
+      </c>
+      <c r="S25" s="16">
+        <v>5.0E-12</v>
+      </c>
+      <c r="T25" s="27"/>
+      <c r="U25" s="27"/>
+      <c r="V25" s="27"/>
+      <c r="W25" s="26" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="X25" s="13" t="str">
+      <c r="X25" s="26" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="Y25" s="17"/>
+      <c r="Y25" s="27"/>
       <c r="Z25" s="6" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="AA25" s="18"/>
-      <c r="AB25" s="17"/>
-      <c r="AC25" s="18"/>
-      <c r="AD25" s="17"/>
+      <c r="AA25" s="28"/>
+      <c r="AB25" s="27"/>
+      <c r="AC25" s="28"/>
+      <c r="AD25" s="27"/>
       <c r="AE25" s="6" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="AF25" s="18"/>
-      <c r="AG25" s="17"/>
-      <c r="AH25" s="18"/>
-      <c r="AI25" s="17"/>
+      <c r="AF25" s="28"/>
+      <c r="AG25" s="27"/>
+      <c r="AH25" s="28"/>
+      <c r="AI25" s="27"/>
       <c r="AJ25" s="6" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="AK25" s="18"/>
-      <c r="AL25" s="19"/>
-      <c r="AM25" s="18"/>
-      <c r="AN25" s="19"/>
+      <c r="AK25" s="28"/>
+      <c r="AL25" s="29"/>
+      <c r="AM25" s="28"/>
+      <c r="AN25" s="29"/>
       <c r="AO25" s="6" t="str">
         <f>IF(OR(AK25="",AL25="",AM25="",AN25=""),"",AK25+(Assumptions!$B$8-AL25)/(AN25-AL25)*(AM25-AK25))</f>
         <v/>
       </c>
-      <c r="AP25" s="18"/>
-      <c r="AQ25" s="19"/>
-      <c r="AR25" s="18"/>
-      <c r="AS25" s="19"/>
+      <c r="AP25" s="28"/>
+      <c r="AQ25" s="29"/>
+      <c r="AR25" s="28"/>
+      <c r="AS25" s="29"/>
       <c r="AT25" s="6" t="str">
         <f>IF(OR(AP25="",AQ25="",AR25="",AS25=""),"",AP25+(Assumptions!$B$9-AQ25)/(AS25-AQ25)*(AR25-AP25))</f>
         <v/>
@@ -7539,7 +8137,18 @@
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="AV25" s="16"/>
+      <c r="AV25" s="23">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AW25" s="23">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="AX25" s="24">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="26" ht="15.75" customHeight="1">
       <c r="A26" s="5">
@@ -7557,25 +8166,25 @@
       <c r="E26" s="5">
         <v>2.0</v>
       </c>
-      <c r="F26" s="8">
+      <c r="F26" s="11">
         <v>303.15</v>
       </c>
-      <c r="G26" s="8">
+      <c r="G26" s="11">
         <v>8.0</v>
       </c>
-      <c r="H26" s="9" t="s">
+      <c r="H26" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="I26" s="9">
+      <c r="I26" s="12">
         <v>550.0</v>
       </c>
-      <c r="J26" s="9">
+      <c r="J26" s="12">
         <v>2750.0</v>
       </c>
-      <c r="K26" s="10">
+      <c r="K26" s="13">
         <v>200000.0</v>
       </c>
-      <c r="L26" s="11">
+      <c r="L26" s="14">
         <f>Assumptions!$B$6</f>
         <v>0.00016558</v>
       </c>
@@ -7595,59 +8204,59 @@
         <f t="shared" si="2"/>
         <v>3504.3975</v>
       </c>
-      <c r="Q26" s="9" t="s">
+      <c r="Q26" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="R26" s="8">
-        <v>2.7</v>
-      </c>
-      <c r="S26" s="10">
-        <v>1.0E-10</v>
-      </c>
-      <c r="T26" s="17"/>
-      <c r="U26" s="17"/>
-      <c r="V26" s="17"/>
-      <c r="W26" s="13" t="str">
+      <c r="R26" s="15">
+        <v>2.68</v>
+      </c>
+      <c r="S26" s="16">
+        <v>6.0E-11</v>
+      </c>
+      <c r="T26" s="27"/>
+      <c r="U26" s="27"/>
+      <c r="V26" s="27"/>
+      <c r="W26" s="26" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="X26" s="13" t="str">
+      <c r="X26" s="26" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="Y26" s="17"/>
+      <c r="Y26" s="27"/>
       <c r="Z26" s="6" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="AA26" s="18"/>
-      <c r="AB26" s="17"/>
-      <c r="AC26" s="18"/>
-      <c r="AD26" s="17"/>
+      <c r="AA26" s="28"/>
+      <c r="AB26" s="27"/>
+      <c r="AC26" s="28"/>
+      <c r="AD26" s="27"/>
       <c r="AE26" s="6" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="AF26" s="18"/>
-      <c r="AG26" s="17"/>
-      <c r="AH26" s="18"/>
-      <c r="AI26" s="17"/>
+      <c r="AF26" s="28"/>
+      <c r="AG26" s="27"/>
+      <c r="AH26" s="28"/>
+      <c r="AI26" s="27"/>
       <c r="AJ26" s="6" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="AK26" s="18"/>
-      <c r="AL26" s="19"/>
-      <c r="AM26" s="18"/>
-      <c r="AN26" s="19"/>
+      <c r="AK26" s="28"/>
+      <c r="AL26" s="29"/>
+      <c r="AM26" s="28"/>
+      <c r="AN26" s="29"/>
       <c r="AO26" s="6" t="str">
         <f>IF(OR(AK26="",AL26="",AM26="",AN26=""),"",AK26+(Assumptions!$B$8-AL26)/(AN26-AL26)*(AM26-AK26))</f>
         <v/>
       </c>
-      <c r="AP26" s="18"/>
-      <c r="AQ26" s="19"/>
-      <c r="AR26" s="18"/>
-      <c r="AS26" s="19"/>
+      <c r="AP26" s="28"/>
+      <c r="AQ26" s="29"/>
+      <c r="AR26" s="28"/>
+      <c r="AS26" s="29"/>
       <c r="AT26" s="6" t="str">
         <f>IF(OR(AP26="",AQ26="",AR26="",AS26=""),"",AP26+(Assumptions!$B$9-AQ26)/(AS26-AQ26)*(AR26-AP26))</f>
         <v/>
@@ -7656,7 +8265,18 @@
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="AV26" s="16"/>
+      <c r="AV26" s="23">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AW26" s="23">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="AX26" s="24">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="27" ht="15.75" customHeight="1">
       <c r="A27" s="5">
@@ -7674,25 +8294,25 @@
       <c r="E27" s="5">
         <v>3.0</v>
       </c>
-      <c r="F27" s="8">
+      <c r="F27" s="11">
         <v>303.15</v>
       </c>
-      <c r="G27" s="8">
+      <c r="G27" s="11">
         <v>8.0</v>
       </c>
-      <c r="H27" s="9" t="s">
+      <c r="H27" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="I27" s="9">
+      <c r="I27" s="12">
         <v>600.0</v>
       </c>
-      <c r="J27" s="9">
+      <c r="J27" s="12">
         <v>2750.0</v>
       </c>
-      <c r="K27" s="10">
+      <c r="K27" s="13">
         <v>204000.0</v>
       </c>
-      <c r="L27" s="11">
+      <c r="L27" s="14">
         <f>Assumptions!$B$6</f>
         <v>0.00016558</v>
       </c>
@@ -7712,59 +8332,59 @@
         <f t="shared" si="2"/>
         <v>3752.07</v>
       </c>
-      <c r="Q27" s="9" t="s">
+      <c r="Q27" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="R27" s="8">
-        <v>2.8</v>
-      </c>
-      <c r="S27" s="10">
-        <v>5.0E-11</v>
-      </c>
-      <c r="T27" s="17"/>
-      <c r="U27" s="17"/>
-      <c r="V27" s="17"/>
-      <c r="W27" s="13" t="str">
+      <c r="R27" s="15">
+        <v>2.77</v>
+      </c>
+      <c r="S27" s="16">
+        <v>2.0E-11</v>
+      </c>
+      <c r="T27" s="27"/>
+      <c r="U27" s="27"/>
+      <c r="V27" s="27"/>
+      <c r="W27" s="26" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="X27" s="13" t="str">
+      <c r="X27" s="26" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="Y27" s="17"/>
+      <c r="Y27" s="27"/>
       <c r="Z27" s="6" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="AA27" s="18"/>
-      <c r="AB27" s="17"/>
-      <c r="AC27" s="18"/>
-      <c r="AD27" s="17"/>
+      <c r="AA27" s="28"/>
+      <c r="AB27" s="27"/>
+      <c r="AC27" s="28"/>
+      <c r="AD27" s="27"/>
       <c r="AE27" s="6" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="AF27" s="18"/>
-      <c r="AG27" s="17"/>
-      <c r="AH27" s="18"/>
-      <c r="AI27" s="17"/>
+      <c r="AF27" s="28"/>
+      <c r="AG27" s="27"/>
+      <c r="AH27" s="28"/>
+      <c r="AI27" s="27"/>
       <c r="AJ27" s="6" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="AK27" s="18"/>
-      <c r="AL27" s="19"/>
-      <c r="AM27" s="18"/>
-      <c r="AN27" s="19"/>
+      <c r="AK27" s="28"/>
+      <c r="AL27" s="29"/>
+      <c r="AM27" s="28"/>
+      <c r="AN27" s="29"/>
       <c r="AO27" s="6" t="str">
         <f>IF(OR(AK27="",AL27="",AM27="",AN27=""),"",AK27+(Assumptions!$B$8-AL27)/(AN27-AL27)*(AM27-AK27))</f>
         <v/>
       </c>
-      <c r="AP27" s="18"/>
-      <c r="AQ27" s="19"/>
-      <c r="AR27" s="18"/>
-      <c r="AS27" s="19"/>
+      <c r="AP27" s="28"/>
+      <c r="AQ27" s="29"/>
+      <c r="AR27" s="28"/>
+      <c r="AS27" s="29"/>
       <c r="AT27" s="6" t="str">
         <f>IF(OR(AP27="",AQ27="",AR27="",AS27=""),"",AP27+(Assumptions!$B$9-AQ27)/(AS27-AQ27)*(AR27-AP27))</f>
         <v/>
@@ -7773,7 +8393,18 @@
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="AV27" s="16"/>
+      <c r="AV27" s="23">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AW27" s="23">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="AX27" s="24">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="28" ht="15.75" customHeight="1">
       <c r="A28" s="5">
@@ -7791,25 +8422,25 @@
       <c r="E28" s="5">
         <v>2.0</v>
       </c>
-      <c r="F28" s="8">
+      <c r="F28" s="11">
         <v>303.15</v>
       </c>
-      <c r="G28" s="8">
+      <c r="G28" s="11">
         <v>12.0</v>
       </c>
-      <c r="H28" s="9" t="s">
+      <c r="H28" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="I28" s="9">
+      <c r="I28" s="12">
         <v>500.0</v>
       </c>
-      <c r="J28" s="9">
+      <c r="J28" s="12">
         <v>2750.0</v>
       </c>
-      <c r="K28" s="10">
+      <c r="K28" s="13">
         <v>186000.0</v>
       </c>
-      <c r="L28" s="11">
+      <c r="L28" s="14">
         <f>Assumptions!$B$6</f>
         <v>0.00016558</v>
       </c>
@@ -7829,59 +8460,59 @@
         <f t="shared" si="2"/>
         <v>3206.725</v>
       </c>
-      <c r="Q28" s="9" t="s">
+      <c r="Q28" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="R28" s="8">
-        <v>2.7</v>
-      </c>
-      <c r="S28" s="10">
-        <v>1.0E-10</v>
-      </c>
-      <c r="T28" s="17"/>
-      <c r="U28" s="17"/>
-      <c r="V28" s="17"/>
-      <c r="W28" s="13" t="str">
+      <c r="R28" s="15">
+        <v>2.68</v>
+      </c>
+      <c r="S28" s="16">
+        <v>2.0E-11</v>
+      </c>
+      <c r="T28" s="27"/>
+      <c r="U28" s="27"/>
+      <c r="V28" s="27"/>
+      <c r="W28" s="26" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="X28" s="13" t="str">
+      <c r="X28" s="26" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="Y28" s="17"/>
+      <c r="Y28" s="27"/>
       <c r="Z28" s="6" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="AA28" s="18"/>
-      <c r="AB28" s="17"/>
-      <c r="AC28" s="18"/>
-      <c r="AD28" s="17"/>
+      <c r="AA28" s="28"/>
+      <c r="AB28" s="27"/>
+      <c r="AC28" s="28"/>
+      <c r="AD28" s="27"/>
       <c r="AE28" s="6" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="AF28" s="18"/>
-      <c r="AG28" s="17"/>
-      <c r="AH28" s="18"/>
-      <c r="AI28" s="17"/>
+      <c r="AF28" s="28"/>
+      <c r="AG28" s="27"/>
+      <c r="AH28" s="28"/>
+      <c r="AI28" s="27"/>
       <c r="AJ28" s="6" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="AK28" s="18"/>
-      <c r="AL28" s="19"/>
-      <c r="AM28" s="18"/>
-      <c r="AN28" s="19"/>
+      <c r="AK28" s="28"/>
+      <c r="AL28" s="29"/>
+      <c r="AM28" s="28"/>
+      <c r="AN28" s="29"/>
       <c r="AO28" s="6" t="str">
         <f>IF(OR(AK28="",AL28="",AM28="",AN28=""),"",AK28+(Assumptions!$B$8-AL28)/(AN28-AL28)*(AM28-AK28))</f>
         <v/>
       </c>
-      <c r="AP28" s="18"/>
-      <c r="AQ28" s="19"/>
-      <c r="AR28" s="18"/>
-      <c r="AS28" s="19"/>
+      <c r="AP28" s="28"/>
+      <c r="AQ28" s="29"/>
+      <c r="AR28" s="28"/>
+      <c r="AS28" s="29"/>
       <c r="AT28" s="6" t="str">
         <f>IF(OR(AP28="",AQ28="",AR28="",AS28=""),"",AP28+(Assumptions!$B$9-AQ28)/(AS28-AQ28)*(AR28-AP28))</f>
         <v/>
@@ -7890,7 +8521,18 @@
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="AV28" s="16"/>
+      <c r="AV28" s="23">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AW28" s="23">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="AX28" s="24">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="29" ht="15.75" customHeight="1">
       <c r="A29" s="5">
@@ -7908,25 +8550,25 @@
       <c r="E29" s="5">
         <v>3.0</v>
       </c>
-      <c r="F29" s="8">
+      <c r="F29" s="11">
         <v>303.15</v>
       </c>
-      <c r="G29" s="8">
+      <c r="G29" s="11">
         <v>12.0</v>
       </c>
-      <c r="H29" s="9" t="s">
+      <c r="H29" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="I29" s="9">
+      <c r="I29" s="12">
         <v>550.0</v>
       </c>
-      <c r="J29" s="9">
+      <c r="J29" s="12">
         <v>2750.0</v>
       </c>
-      <c r="K29" s="10">
+      <c r="K29" s="13">
         <v>200000.0</v>
       </c>
-      <c r="L29" s="11">
+      <c r="L29" s="14">
         <f>Assumptions!$B$6</f>
         <v>0.00016558</v>
       </c>
@@ -7946,59 +8588,59 @@
         <f t="shared" si="2"/>
         <v>3504.3975</v>
       </c>
-      <c r="Q29" s="9" t="s">
+      <c r="Q29" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="R29" s="8">
-        <v>2.8</v>
-      </c>
-      <c r="S29" s="10">
-        <v>5.0E-11</v>
-      </c>
-      <c r="T29" s="17"/>
-      <c r="U29" s="17"/>
-      <c r="V29" s="17"/>
-      <c r="W29" s="13" t="str">
+      <c r="R29" s="15">
+        <v>2.77</v>
+      </c>
+      <c r="S29" s="16">
+        <v>5.0E-12</v>
+      </c>
+      <c r="T29" s="27"/>
+      <c r="U29" s="27"/>
+      <c r="V29" s="27"/>
+      <c r="W29" s="26" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="X29" s="13" t="str">
+      <c r="X29" s="26" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="Y29" s="17"/>
+      <c r="Y29" s="27"/>
       <c r="Z29" s="6" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="AA29" s="18"/>
-      <c r="AB29" s="17"/>
-      <c r="AC29" s="18"/>
-      <c r="AD29" s="17"/>
+      <c r="AA29" s="28"/>
+      <c r="AB29" s="27"/>
+      <c r="AC29" s="28"/>
+      <c r="AD29" s="27"/>
       <c r="AE29" s="6" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="AF29" s="18"/>
-      <c r="AG29" s="17"/>
-      <c r="AH29" s="18"/>
-      <c r="AI29" s="17"/>
+      <c r="AF29" s="28"/>
+      <c r="AG29" s="27"/>
+      <c r="AH29" s="28"/>
+      <c r="AI29" s="27"/>
       <c r="AJ29" s="6" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="AK29" s="18"/>
-      <c r="AL29" s="19"/>
-      <c r="AM29" s="18"/>
-      <c r="AN29" s="19"/>
+      <c r="AK29" s="28"/>
+      <c r="AL29" s="29"/>
+      <c r="AM29" s="28"/>
+      <c r="AN29" s="29"/>
       <c r="AO29" s="6" t="str">
         <f>IF(OR(AK29="",AL29="",AM29="",AN29=""),"",AK29+(Assumptions!$B$8-AL29)/(AN29-AL29)*(AM29-AK29))</f>
         <v/>
       </c>
-      <c r="AP29" s="18"/>
-      <c r="AQ29" s="19"/>
-      <c r="AR29" s="18"/>
-      <c r="AS29" s="19"/>
+      <c r="AP29" s="28"/>
+      <c r="AQ29" s="29"/>
+      <c r="AR29" s="28"/>
+      <c r="AS29" s="29"/>
       <c r="AT29" s="6" t="str">
         <f>IF(OR(AP29="",AQ29="",AR29="",AS29=""),"",AP29+(Assumptions!$B$9-AQ29)/(AS29-AQ29)*(AR29-AP29))</f>
         <v/>
@@ -8007,7 +8649,18 @@
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="AV29" s="16"/>
+      <c r="AV29" s="23">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AW29" s="23">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="AX29" s="24">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="30" ht="15.75" customHeight="1">
       <c r="A30" s="5">
@@ -8025,25 +8678,25 @@
       <c r="E30" s="5">
         <v>1.0</v>
       </c>
-      <c r="F30" s="8">
+      <c r="F30" s="11">
         <v>303.15</v>
       </c>
-      <c r="G30" s="8">
+      <c r="G30" s="11">
         <v>12.0</v>
       </c>
-      <c r="H30" s="9" t="s">
+      <c r="H30" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="I30" s="9">
+      <c r="I30" s="12">
         <v>600.0</v>
       </c>
-      <c r="J30" s="9">
+      <c r="J30" s="12">
         <v>2750.0</v>
       </c>
-      <c r="K30" s="10">
+      <c r="K30" s="13">
         <v>204000.0</v>
       </c>
-      <c r="L30" s="11">
+      <c r="L30" s="14">
         <f>Assumptions!$B$6</f>
         <v>0.00016558</v>
       </c>
@@ -8063,59 +8716,59 @@
         <f t="shared" si="2"/>
         <v>3752.07</v>
       </c>
-      <c r="Q30" s="9" t="s">
+      <c r="Q30" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="R30" s="8">
-        <v>2.6</v>
-      </c>
-      <c r="S30" s="10">
-        <v>2.0E-10</v>
-      </c>
-      <c r="T30" s="17"/>
-      <c r="U30" s="17"/>
-      <c r="V30" s="17"/>
-      <c r="W30" s="13" t="str">
+      <c r="R30" s="15">
+        <v>2.58</v>
+      </c>
+      <c r="S30" s="16">
+        <v>6.0E-11</v>
+      </c>
+      <c r="T30" s="27"/>
+      <c r="U30" s="27"/>
+      <c r="V30" s="27"/>
+      <c r="W30" s="26" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="X30" s="13" t="str">
+      <c r="X30" s="26" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="Y30" s="17"/>
+      <c r="Y30" s="27"/>
       <c r="Z30" s="6" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="AA30" s="18"/>
-      <c r="AB30" s="17"/>
-      <c r="AC30" s="18"/>
-      <c r="AD30" s="17"/>
+      <c r="AA30" s="28"/>
+      <c r="AB30" s="27"/>
+      <c r="AC30" s="28"/>
+      <c r="AD30" s="27"/>
       <c r="AE30" s="6" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="AF30" s="18"/>
-      <c r="AG30" s="17"/>
-      <c r="AH30" s="18"/>
-      <c r="AI30" s="17"/>
+      <c r="AF30" s="28"/>
+      <c r="AG30" s="27"/>
+      <c r="AH30" s="28"/>
+      <c r="AI30" s="27"/>
       <c r="AJ30" s="6" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="AK30" s="18"/>
-      <c r="AL30" s="19"/>
-      <c r="AM30" s="18"/>
-      <c r="AN30" s="19"/>
+      <c r="AK30" s="28"/>
+      <c r="AL30" s="29"/>
+      <c r="AM30" s="28"/>
+      <c r="AN30" s="29"/>
       <c r="AO30" s="6" t="str">
         <f>IF(OR(AK30="",AL30="",AM30="",AN30=""),"",AK30+(Assumptions!$B$8-AL30)/(AN30-AL30)*(AM30-AK30))</f>
         <v/>
       </c>
-      <c r="AP30" s="18"/>
-      <c r="AQ30" s="19"/>
-      <c r="AR30" s="18"/>
-      <c r="AS30" s="19"/>
+      <c r="AP30" s="28"/>
+      <c r="AQ30" s="29"/>
+      <c r="AR30" s="28"/>
+      <c r="AS30" s="29"/>
       <c r="AT30" s="6" t="str">
         <f>IF(OR(AP30="",AQ30="",AR30="",AS30=""),"",AP30+(Assumptions!$B$9-AQ30)/(AS30-AQ30)*(AR30-AP30))</f>
         <v/>
@@ -8124,7 +8777,18 @@
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="AV30" s="16"/>
+      <c r="AV30" s="23">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AW30" s="23">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="AX30" s="24">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="31" ht="15.75" customHeight="1"/>
     <row r="32" ht="15.75" customHeight="1"/>
@@ -9098,7 +9762,7 @@
     <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:AV1"/>
+    <mergeCell ref="A1:AU1"/>
   </mergeCells>
   <printOptions/>
   <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
@@ -9124,8 +9788,8 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="20" t="s">
-        <v>142</v>
+      <c r="A1" s="1" t="s">
+        <v>146</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -9134,40 +9798,40 @@
       <c r="F1" s="3"/>
     </row>
     <row r="3">
-      <c r="A3" s="21" t="s">
-        <v>143</v>
-      </c>
-      <c r="B3" s="21" t="s">
-        <v>144</v>
-      </c>
-      <c r="C3" s="21" t="s">
-        <v>145</v>
-      </c>
-      <c r="D3" s="21" t="s">
-        <v>146</v>
-      </c>
-      <c r="E3" s="21" t="s">
+      <c r="A3" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="F3" s="21" t="s">
+      <c r="B3" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="F3" s="4" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="C4" s="5" t="s">
         <v>43</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="F4" s="5" t="s">
         <v>41</v>
@@ -9175,19 +9839,19 @@
     </row>
     <row r="5">
       <c r="A5" s="5" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="C5" s="5" t="s">
         <v>43</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="F5" s="5" t="s">
         <v>41</v>
@@ -9195,19 +9859,19 @@
     </row>
     <row r="6">
       <c r="A6" s="5" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="C6" s="5" t="s">
         <v>43</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="F6" s="5" t="s">
         <v>41</v>
@@ -9215,22 +9879,35 @@
     </row>
     <row r="7">
       <c r="A7" s="5" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="F7" s="5" t="s">
         <v>41</v>
+      </c>
+    </row>
+    <row r="12" ht="283.5" customHeight="1">
+      <c r="B12" s="30" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="31" t="s">
+        <v>170</v>
+      </c>
+      <c r="E15" s="32" t="s">
+        <v>171</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1"/>
@@ -10214,12 +10891,18 @@
     <row r="999" ht="15.75" customHeight="1"/>
     <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="4">
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="B12:E12"/>
+    <mergeCell ref="B15:D28"/>
+    <mergeCell ref="E15:H28"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink r:id="rId1" ref="E15"/>
+  </hyperlinks>
   <printOptions/>
   <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
   <pageSetup orientation="landscape"/>
-  <drawing r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>